--- a/DOCUMENTACION_PROYECTO/Presupuesto de Proyecto.xlsx
+++ b/DOCUMENTACION_PROYECTO/Presupuesto de Proyecto.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30023"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marce\Downloads\Modulo Proyectos-20260213T224249Z-3-001\Modulo Proyectos\Sesion 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{77FD0F9A-966F-42FF-B581-A06A7A296C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2929EE34-DA6D-438A-BA81-1C3D54C9308B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="98">
+  <si>
+    <t>cc</t>
+  </si>
   <si>
     <t>Presupuesto de Proyecto</t>
   </si>
@@ -132,16 +135,13 @@
     <t>Definir la lógica del sistema, y con base en ello definir los requerimientos mínimos.</t>
   </si>
   <si>
-    <t>En Progreso</t>
+    <t>Aprobado</t>
   </si>
   <si>
     <t>Diseño de arquitectura</t>
   </si>
   <si>
     <t>Definir la estructura del backend.</t>
-  </si>
-  <si>
-    <t>No Iniciado</t>
   </si>
   <si>
     <t>Diseño de base de datos</t>
@@ -186,6 +186,9 @@
     <t>Realizar todo el proceso de documentación técnica del proyecto.</t>
   </si>
   <si>
+    <t>En Progreso</t>
+  </si>
+  <si>
     <t>Despliegue</t>
   </si>
   <si>
@@ -214,6 +217,9 @@
   </si>
   <si>
     <t>Durante esta actividad se definen los problemas que busca resolver la plataforma, los tipos de usuarios que interactuarán con ella (administradores, técnicos y usuarios finales) y los procesos actuales de gestión de incidencias dentro de la empresa.</t>
+  </si>
+  <si>
+    <t>Completo</t>
   </si>
   <si>
     <t>Diseño de wireframes</t>
@@ -288,6 +294,9 @@
     <t>Verificación de funcionamiento</t>
   </si>
   <si>
+    <t>No Iniciado</t>
+  </si>
+  <si>
     <t>Optimización de rendimiento</t>
   </si>
   <si>
@@ -330,13 +339,7 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>Completo</t>
-  </si>
-  <si>
     <t>Requiere Revisión</t>
-  </si>
-  <si>
-    <t>Aprobado</t>
   </si>
   <si>
     <t>Atrasado</t>
@@ -617,7 +620,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="50">
+  <borders count="49">
     <border>
       <left/>
       <right/>
@@ -1169,17 +1172,6 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color theme="2" tint="-9.9978637043366805E-2"/>
       </left>
       <right/>
@@ -1229,7 +1221,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="182">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1680,17 +1672,11 @@
     <xf numFmtId="165" fontId="11" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="20" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="20" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1708,23 +1694,23 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="47" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="46" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="12" fillId="5" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="12" fillId="5" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="168" fontId="19" fillId="5" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="168" fontId="19" fillId="5" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="16" fontId="20" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="20" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1794,14 +1780,45 @@
     <xf numFmtId="0" fontId="11" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="168" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="5" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="8">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
-    <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="5" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="3" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="6" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="3" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="4" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="5" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="2" builtinId="9" hidden="1"/>
+    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="7" xr:uid="{096755C3-0BB5-E94E-8E6C-945830891248}"/>
   </cellStyles>
@@ -2406,8 +2423,8 @@
     <tabColor theme="3" tint="0.59999389629810485"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AO407"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5"/>
+  <dimension ref="A1:AO408"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="52.25" style="2" customWidth="1"/>
@@ -2424,14 +2441,16 @@
     <col min="16" max="16" width="14" style="55" customWidth="1"/>
     <col min="17" max="18" width="12.875" style="55" customWidth="1"/>
     <col min="19" max="19" width="22.75" style="2" customWidth="1"/>
-    <col min="20" max="20" width="3.125" style="2" customWidth="1"/>
-    <col min="21" max="16384" width="11" style="2"/>
+    <col min="20" max="20" width="3.125" style="2" hidden="1" customWidth="1"/>
+    <col min="21" max="16384" width="0" style="2" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="45" customHeight="1">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="26" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="83"/>
       <c r="D1" s="14"/>
@@ -2481,26 +2500,26 @@
       <c r="E2" s="28"/>
       <c r="F2" s="28"/>
       <c r="G2" s="29"/>
-      <c r="H2" s="159" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="160"/>
-      <c r="J2" s="160"/>
-      <c r="K2" s="160" t="s">
+      <c r="H2" s="157" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="160"/>
-      <c r="M2" s="160"/>
-      <c r="N2" s="161" t="s">
+      <c r="I2" s="158"/>
+      <c r="J2" s="158"/>
+      <c r="K2" s="158" t="s">
         <v>3</v>
       </c>
-      <c r="O2" s="162"/>
-      <c r="P2" s="163"/>
-      <c r="Q2" s="164" t="s">
+      <c r="L2" s="158"/>
+      <c r="M2" s="158"/>
+      <c r="N2" s="159" t="s">
         <v>4</v>
       </c>
-      <c r="R2" s="165"/>
-      <c r="S2" s="166"/>
+      <c r="O2" s="160"/>
+      <c r="P2" s="161"/>
+      <c r="Q2" s="162" t="s">
+        <v>5</v>
+      </c>
+      <c r="R2" s="163"/>
+      <c r="S2" s="164"/>
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
       <c r="V2" s="4"/>
@@ -2527,58 +2546,58 @@
     <row r="3" spans="1:41" s="5" customFormat="1" ht="35.1" customHeight="1">
       <c r="A3" s="4"/>
       <c r="B3" s="61" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="61" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="61" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3" s="30" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H3" s="49" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I3" s="57" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M3" s="110" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N3" s="110" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O3" s="110" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P3" s="109" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q3" s="108" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R3" s="107" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S3" s="116" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
@@ -2606,7 +2625,7 @@
     <row r="4" spans="1:41" s="5" customFormat="1" ht="30" customHeight="1">
       <c r="A4" s="4"/>
       <c r="B4" s="62" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
@@ -2651,13 +2670,13 @@
     <row r="5" spans="1:41" s="5" customFormat="1" ht="47.25" customHeight="1">
       <c r="A5" s="4"/>
       <c r="B5" s="27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="118" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5" s="130">
         <v>46101</v>
@@ -2672,11 +2691,11 @@
         <v>10</v>
       </c>
       <c r="I5" s="66">
-        <v>40000</v>
+        <v>50000</v>
       </c>
       <c r="J5" s="67">
         <f>H5*I5</f>
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="K5" s="87">
         <v>1</v>
@@ -2702,11 +2721,11 @@
       </c>
       <c r="R5" s="96">
         <f>J5+M5+N5+O5+P5</f>
-        <v>440000</v>
+        <v>540000</v>
       </c>
       <c r="S5" s="115">
         <f t="shared" ref="S5:S14" si="0">R5-Q5</f>
-        <v>-10000</v>
+        <v>90000</v>
       </c>
       <c r="T5" s="4"/>
       <c r="U5" s="4"/>
@@ -2734,13 +2753,13 @@
     <row r="6" spans="1:41" s="5" customFormat="1" ht="30" customHeight="1">
       <c r="A6" s="4"/>
       <c r="B6" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="118" t="s">
         <v>27</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="118" t="s">
-        <v>29</v>
       </c>
       <c r="E6" s="126">
         <v>46103</v>
@@ -2755,11 +2774,11 @@
         <v>12</v>
       </c>
       <c r="I6" s="66">
-        <v>40000</v>
+        <v>42000</v>
       </c>
       <c r="J6" s="67">
         <f t="shared" ref="J6:J17" si="1">H6*I6</f>
-        <v>480000</v>
+        <v>504000</v>
       </c>
       <c r="K6" s="87">
         <v>1</v>
@@ -2785,11 +2804,11 @@
       </c>
       <c r="R6" s="96">
         <f t="shared" ref="R6:S14" si="3">J6+M6+N6+O6+P6</f>
-        <v>510000</v>
+        <v>534000</v>
       </c>
       <c r="S6" s="115">
         <f t="shared" si="0"/>
-        <v>10000</v>
+        <v>34000</v>
       </c>
       <c r="T6" s="4"/>
       <c r="U6" s="4"/>
@@ -2823,7 +2842,7 @@
         <v>31</v>
       </c>
       <c r="D7" s="118" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E7" s="124">
         <v>46105</v>
@@ -2906,7 +2925,7 @@
         <v>33</v>
       </c>
       <c r="D8" s="118" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E8" s="125">
         <v>46131</v>
@@ -2921,11 +2940,11 @@
         <v>12</v>
       </c>
       <c r="I8" s="66">
-        <v>40000</v>
+        <v>32000</v>
       </c>
       <c r="J8" s="67">
         <f t="shared" si="1"/>
-        <v>480000</v>
+        <v>384000</v>
       </c>
       <c r="K8" s="87">
         <v>1</v>
@@ -2951,11 +2970,11 @@
       </c>
       <c r="R8" s="96">
         <f t="shared" si="3"/>
-        <v>510000</v>
+        <v>414000</v>
       </c>
       <c r="S8" s="115">
         <f t="shared" si="0"/>
-        <v>10000</v>
+        <v>-86000</v>
       </c>
       <c r="T8" s="4"/>
       <c r="U8" s="4"/>
@@ -2989,7 +3008,7 @@
         <v>35</v>
       </c>
       <c r="D9" s="118" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E9" s="124">
         <v>46132</v>
@@ -3072,7 +3091,7 @@
         <v>37</v>
       </c>
       <c r="D10" s="118" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E10" s="122">
         <v>46133</v>
@@ -3087,11 +3106,11 @@
         <v>35</v>
       </c>
       <c r="I10" s="66">
-        <v>40000</v>
+        <v>38500</v>
       </c>
       <c r="J10" s="67">
         <f t="shared" si="1"/>
-        <v>1400000</v>
+        <v>1347500</v>
       </c>
       <c r="K10" s="87">
         <v>1</v>
@@ -3117,11 +3136,11 @@
       </c>
       <c r="R10" s="96">
         <f t="shared" si="3"/>
-        <v>1430000</v>
+        <v>1377500</v>
       </c>
       <c r="S10" s="115">
         <f t="shared" si="0"/>
-        <v>30000</v>
+        <v>-22500</v>
       </c>
       <c r="T10" s="4"/>
       <c r="U10" s="4"/>
@@ -3154,10 +3173,10 @@
       <c r="C11" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="142" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="143">
+      <c r="D11" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="141">
         <v>46134</v>
       </c>
       <c r="F11" s="128">
@@ -3234,11 +3253,11 @@
       <c r="B12" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="141" t="s">
+      <c r="C12" s="140" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="140" t="s">
-        <v>29</v>
+      <c r="D12" s="118" t="s">
+        <v>27</v>
       </c>
       <c r="E12" s="125">
         <v>46135</v>
@@ -3317,11 +3336,11 @@
       <c r="B13" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="141" t="s">
+      <c r="C13" s="140" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="140" t="s">
-        <v>29</v>
+      <c r="D13" s="118" t="s">
+        <v>44</v>
       </c>
       <c r="E13" s="125">
         <v>46135</v>
@@ -3332,7 +3351,7 @@
       <c r="G13" s="137">
         <v>46145</v>
       </c>
-      <c r="H13" s="148">
+      <c r="H13" s="146">
         <v>8</v>
       </c>
       <c r="I13" s="66">
@@ -3398,13 +3417,13 @@
     <row r="14" spans="1:41" s="5" customFormat="1" ht="30" customHeight="1">
       <c r="A14" s="4"/>
       <c r="B14" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="140" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="118" t="s">
         <v>44</v>
-      </c>
-      <c r="C14" s="141" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="140" t="s">
-        <v>29</v>
       </c>
       <c r="E14" s="125">
         <v>46137</v>
@@ -3415,15 +3434,15 @@
       <c r="G14" s="125">
         <v>46148</v>
       </c>
-      <c r="H14" s="145">
+      <c r="H14" s="143">
         <v>6</v>
       </c>
       <c r="I14" s="85">
-        <v>40000</v>
+        <v>45000</v>
       </c>
       <c r="J14" s="67">
         <f t="shared" si="1"/>
-        <v>240000</v>
+        <v>270000</v>
       </c>
       <c r="K14" s="87">
         <v>1</v>
@@ -3449,11 +3468,11 @@
       </c>
       <c r="R14" s="96">
         <f t="shared" si="3"/>
-        <v>290000</v>
+        <v>320000</v>
       </c>
       <c r="S14" s="115">
         <f t="shared" si="0"/>
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="T14" s="4"/>
       <c r="U14" s="4"/>
@@ -3481,27 +3500,27 @@
     <row r="15" spans="1:41" s="5" customFormat="1" ht="52.5" customHeight="1">
       <c r="A15" s="4"/>
       <c r="B15" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="141" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="140" t="s">
-        <v>29</v>
+      <c r="C15" s="140" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="118" t="s">
+        <v>27</v>
       </c>
       <c r="E15" s="125">
         <v>46138</v>
       </c>
-      <c r="F15" s="152">
+      <c r="F15" s="150">
         <v>46144</v>
       </c>
       <c r="G15" s="125">
         <v>46149</v>
       </c>
-      <c r="H15" s="145">
+      <c r="H15" s="143">
         <v>1</v>
       </c>
-      <c r="I15" s="149">
+      <c r="I15" s="147">
         <v>500000</v>
       </c>
       <c r="J15" s="67">
@@ -3564,13 +3583,13 @@
     <row r="16" spans="1:41" s="5" customFormat="1" ht="71.25" customHeight="1">
       <c r="A16" s="4"/>
       <c r="B16" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="141" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="140" t="s">
-        <v>29</v>
+      <c r="C16" s="140" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="118" t="s">
+        <v>44</v>
       </c>
       <c r="E16" s="126">
         <v>46139</v>
@@ -3581,15 +3600,15 @@
       <c r="G16" s="131">
         <v>46150</v>
       </c>
-      <c r="H16" s="153">
-        <v>1</v>
-      </c>
-      <c r="I16" s="146">
-        <v>1200000</v>
-      </c>
-      <c r="J16" s="147">
+      <c r="H16" s="151">
+        <v>3</v>
+      </c>
+      <c r="I16" s="144">
+        <v>300000</v>
+      </c>
+      <c r="J16" s="145">
         <f t="shared" si="1"/>
-        <v>1200000</v>
+        <v>900000</v>
       </c>
       <c r="K16" s="87">
         <v>1</v>
@@ -3615,11 +3634,11 @@
       </c>
       <c r="R16" s="96">
         <f>J16+M16+N16+O16+P16</f>
-        <v>6235000</v>
+        <v>5935000</v>
       </c>
       <c r="S16" s="115">
         <f>R16-Q16</f>
-        <v>-765000</v>
+        <v>-1065000</v>
       </c>
       <c r="T16" s="4"/>
       <c r="U16" s="4"/>
@@ -3647,24 +3666,24 @@
     <row r="17" spans="1:41" s="5" customFormat="1" ht="30" customHeight="1">
       <c r="A17" s="4"/>
       <c r="B17" s="59" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C17" s="59"/>
-      <c r="D17" s="144"/>
+      <c r="D17" s="142"/>
       <c r="E17" s="138"/>
       <c r="F17" s="138"/>
       <c r="G17" s="139"/>
-      <c r="H17" s="150">
+      <c r="H17" s="148">
         <f>SUM(H5:H16)</f>
-        <v>172</v>
-      </c>
-      <c r="I17" s="151">
+        <v>174</v>
+      </c>
+      <c r="I17" s="149">
         <f>SUM(I5:I16)</f>
-        <v>2120000</v>
+        <v>1227500</v>
       </c>
       <c r="J17" s="60">
         <f>SUM(J5:J16)</f>
-        <v>9500000</v>
+        <v>9205500</v>
       </c>
       <c r="K17" s="88"/>
       <c r="L17" s="60"/>
@@ -3690,11 +3709,11 @@
       </c>
       <c r="R17" s="101">
         <f>SUM(J17:P17)</f>
-        <v>14984000</v>
+        <v>14689500</v>
       </c>
       <c r="S17" s="114">
         <f>R17-Q17</f>
-        <v>-1221000</v>
+        <v>-1515500</v>
       </c>
       <c r="T17" s="4"/>
       <c r="U17" s="4"/>
@@ -3770,26 +3789,26 @@
       <c r="E19" s="28"/>
       <c r="F19" s="28"/>
       <c r="G19" s="29"/>
-      <c r="H19" s="167" t="s">
-        <v>1</v>
-      </c>
-      <c r="I19" s="168"/>
-      <c r="J19" s="168"/>
-      <c r="K19" s="168" t="s">
+      <c r="H19" s="165" t="s">
         <v>2</v>
       </c>
-      <c r="L19" s="168"/>
-      <c r="M19" s="168"/>
-      <c r="N19" s="169" t="s">
+      <c r="I19" s="166"/>
+      <c r="J19" s="166"/>
+      <c r="K19" s="166" t="s">
         <v>3</v>
       </c>
-      <c r="O19" s="170"/>
-      <c r="P19" s="171"/>
-      <c r="Q19" s="172" t="s">
+      <c r="L19" s="166"/>
+      <c r="M19" s="166"/>
+      <c r="N19" s="167" t="s">
         <v>4</v>
       </c>
-      <c r="R19" s="173"/>
-      <c r="S19" s="174"/>
+      <c r="O19" s="168"/>
+      <c r="P19" s="169"/>
+      <c r="Q19" s="170" t="s">
+        <v>5</v>
+      </c>
+      <c r="R19" s="171"/>
+      <c r="S19" s="172"/>
       <c r="T19" s="4"/>
       <c r="U19" s="4"/>
       <c r="V19" s="4"/>
@@ -3816,58 +3835,58 @@
     <row r="20" spans="1:41" s="5" customFormat="1" ht="35.1" customHeight="1">
       <c r="A20" s="4"/>
       <c r="B20" s="36" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H20" s="51" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I20" s="58" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J20" s="37" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K20" s="37" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L20" s="37" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M20" s="98" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N20" s="98" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O20" s="98" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P20" s="98" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q20" s="98" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R20" s="98" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S20" s="113" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T20" s="4"/>
       <c r="U20" s="4"/>
@@ -3895,7 +3914,7 @@
     <row r="21" spans="1:41" s="5" customFormat="1" ht="30" customHeight="1">
       <c r="A21" s="4"/>
       <c r="B21" s="38" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C21" s="38"/>
       <c r="D21" s="38"/>
@@ -3905,7 +3924,7 @@
       <c r="H21" s="73"/>
       <c r="I21" s="74"/>
       <c r="J21" s="40"/>
-      <c r="K21" s="155"/>
+      <c r="K21" s="153"/>
       <c r="L21" s="40"/>
       <c r="M21" s="54"/>
       <c r="N21" s="54"/>
@@ -3940,13 +3959,13 @@
     <row r="22" spans="1:41" s="5" customFormat="1" ht="88.5" customHeight="1">
       <c r="A22" s="4"/>
       <c r="B22" s="44" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C22" s="44" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D22" s="42" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="E22" s="111">
         <v>46101</v>
@@ -3958,40 +3977,40 @@
         <v>46108</v>
       </c>
       <c r="H22" s="52">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I22" s="75">
         <v>35000</v>
       </c>
       <c r="J22" s="43">
         <f>H22*I22</f>
-        <v>280000</v>
-      </c>
-      <c r="K22" s="157">
+        <v>350000</v>
+      </c>
+      <c r="K22" s="155">
         <v>1</v>
       </c>
-      <c r="L22" s="158">
+      <c r="L22" s="156">
         <v>30000</v>
       </c>
-      <c r="M22" s="158">
+      <c r="M22" s="156">
         <v>30000</v>
       </c>
-      <c r="N22" s="158">
+      <c r="N22" s="156">
         <v>0</v>
       </c>
-      <c r="O22" s="158">
+      <c r="O22" s="156">
         <v>15000</v>
       </c>
-      <c r="P22" s="158">
+      <c r="P22" s="156">
         <v>10000</v>
       </c>
-      <c r="Q22" s="158">
+      <c r="Q22" s="156">
         <v>595000</v>
       </c>
-      <c r="R22" s="158">
+      <c r="R22" s="156">
         <v>570000</v>
       </c>
-      <c r="S22" s="156">
+      <c r="S22" s="154">
         <f>Q22-R22</f>
         <v>25000</v>
       </c>
@@ -4021,13 +4040,13 @@
     <row r="23" spans="1:41" s="5" customFormat="1" ht="36.75">
       <c r="A23" s="4"/>
       <c r="B23" s="44" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C23" s="44" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D23" s="42" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E23" s="111">
         <v>46103</v>
@@ -4036,43 +4055,43 @@
         <v>46108</v>
       </c>
       <c r="G23" s="111">
-        <v>46111</v>
+        <v>46147</v>
       </c>
       <c r="H23" s="52">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I23" s="75">
         <v>35000</v>
       </c>
       <c r="J23" s="43">
         <f t="shared" ref="J23:J28" si="4">H23*I23</f>
-        <v>420000</v>
-      </c>
-      <c r="K23" s="157">
+        <v>560000</v>
+      </c>
+      <c r="K23" s="155">
         <v>1</v>
       </c>
-      <c r="L23" s="158">
+      <c r="L23" s="156">
         <v>40000</v>
       </c>
-      <c r="M23" s="158">
+      <c r="M23" s="156">
         <v>40000</v>
       </c>
-      <c r="N23" s="158">
+      <c r="N23" s="156">
         <v>0</v>
       </c>
-      <c r="O23" s="158">
+      <c r="O23" s="156">
         <v>15000</v>
       </c>
-      <c r="P23" s="158">
+      <c r="P23" s="156">
         <v>10000</v>
       </c>
-      <c r="Q23" s="158">
+      <c r="Q23" s="156">
         <v>650000</v>
       </c>
-      <c r="R23" s="158">
+      <c r="R23" s="156">
         <v>630000</v>
       </c>
-      <c r="S23" s="156">
+      <c r="S23" s="154">
         <f>R23-Q23</f>
         <v>-20000</v>
       </c>
@@ -4102,13 +4121,13 @@
     <row r="24" spans="1:41" s="5" customFormat="1" ht="73.5">
       <c r="A24" s="4"/>
       <c r="B24" s="44" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C24" s="44" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D24" s="42" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E24" s="111">
         <v>46105</v>
@@ -4129,31 +4148,31 @@
         <f t="shared" si="4"/>
         <v>560000</v>
       </c>
-      <c r="K24" s="157">
+      <c r="K24" s="155">
         <v>1</v>
       </c>
-      <c r="L24" s="158">
+      <c r="L24" s="156">
         <v>80000</v>
       </c>
-      <c r="M24" s="158">
+      <c r="M24" s="156">
         <v>80000</v>
       </c>
-      <c r="N24" s="158">
+      <c r="N24" s="156">
         <v>0</v>
       </c>
-      <c r="O24" s="158">
+      <c r="O24" s="156">
         <v>20000</v>
       </c>
-      <c r="P24" s="158">
+      <c r="P24" s="156">
         <v>20000</v>
       </c>
-      <c r="Q24" s="158">
+      <c r="Q24" s="156">
         <v>1500000</v>
       </c>
-      <c r="R24" s="158">
+      <c r="R24" s="156">
         <v>1250000</v>
       </c>
-      <c r="S24" s="156">
+      <c r="S24" s="154">
         <f>R24-Q24</f>
         <v>-250000</v>
       </c>
@@ -4183,13 +4202,13 @@
     <row r="25" spans="1:41" s="5" customFormat="1" ht="48" customHeight="1">
       <c r="A25" s="4"/>
       <c r="B25" s="82" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D25" s="42" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E25" s="111">
         <v>46131</v>
@@ -4198,43 +4217,43 @@
         <v>46134</v>
       </c>
       <c r="G25" s="111">
-        <v>46135</v>
+        <v>46147</v>
       </c>
       <c r="H25" s="52">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I25" s="75">
         <v>35000</v>
       </c>
       <c r="J25" s="43">
         <f t="shared" si="4"/>
-        <v>210000</v>
-      </c>
-      <c r="K25" s="157">
+        <v>700000</v>
+      </c>
+      <c r="K25" s="155">
         <v>1</v>
       </c>
-      <c r="L25" s="158">
+      <c r="L25" s="156">
         <v>20000</v>
       </c>
-      <c r="M25" s="158">
+      <c r="M25" s="156">
         <v>20000</v>
       </c>
-      <c r="N25" s="158">
+      <c r="N25" s="156">
         <v>0</v>
       </c>
-      <c r="O25" s="158">
+      <c r="O25" s="156">
         <v>15000</v>
       </c>
-      <c r="P25" s="158">
+      <c r="P25" s="156">
         <v>10000</v>
       </c>
-      <c r="Q25" s="158">
+      <c r="Q25" s="156">
         <v>450000</v>
       </c>
-      <c r="R25" s="158">
+      <c r="R25" s="156">
         <v>430000</v>
       </c>
-      <c r="S25" s="156">
+      <c r="S25" s="154">
         <f>R25-Q25</f>
         <v>-20000</v>
       </c>
@@ -4264,13 +4283,13 @@
     <row r="26" spans="1:41" s="5" customFormat="1" ht="52.5" customHeight="1">
       <c r="A26" s="4"/>
       <c r="B26" s="44" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C26" s="44" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D26" s="42" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="E26" s="111">
         <v>46132</v>
@@ -4282,40 +4301,40 @@
         <v>46140</v>
       </c>
       <c r="H26" s="52">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I26" s="75">
         <v>35000</v>
       </c>
       <c r="J26" s="43">
         <f t="shared" si="4"/>
-        <v>420000</v>
-      </c>
-      <c r="K26" s="157">
+        <v>350000</v>
+      </c>
+      <c r="K26" s="155">
         <v>1</v>
       </c>
-      <c r="L26" s="158">
+      <c r="L26" s="156">
         <v>50000</v>
       </c>
-      <c r="M26" s="158">
+      <c r="M26" s="156">
         <v>50000</v>
       </c>
-      <c r="N26" s="158">
+      <c r="N26" s="156">
         <v>0</v>
       </c>
-      <c r="O26" s="158">
+      <c r="O26" s="156">
         <v>20000</v>
       </c>
-      <c r="P26" s="158">
+      <c r="P26" s="156">
         <v>15000</v>
       </c>
-      <c r="Q26" s="158">
+      <c r="Q26" s="156">
         <v>885000</v>
       </c>
-      <c r="R26" s="158">
+      <c r="R26" s="156">
         <v>880000</v>
       </c>
-      <c r="S26" s="156">
+      <c r="S26" s="154">
         <f>R26-Q26</f>
         <v>-5000</v>
       </c>
@@ -4345,13 +4364,13 @@
     <row r="27" spans="1:41" s="5" customFormat="1" ht="30" customHeight="1">
       <c r="A27" s="4"/>
       <c r="B27" s="44" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C27" s="44" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D27" s="42" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="E27" s="111">
         <v>46133</v>
@@ -4363,40 +4382,40 @@
         <v>46142</v>
       </c>
       <c r="H27" s="52">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I27" s="75">
         <v>35000</v>
       </c>
       <c r="J27" s="43">
         <f t="shared" si="4"/>
-        <v>700000</v>
-      </c>
-      <c r="K27" s="157">
+        <v>210000</v>
+      </c>
+      <c r="K27" s="155">
         <v>1</v>
       </c>
-      <c r="L27" s="158">
+      <c r="L27" s="156">
         <v>50000</v>
       </c>
-      <c r="M27" s="158">
+      <c r="M27" s="156">
         <v>50000</v>
       </c>
-      <c r="N27" s="158">
+      <c r="N27" s="156">
         <v>0</v>
       </c>
-      <c r="O27" s="158">
+      <c r="O27" s="156">
         <v>20000</v>
       </c>
-      <c r="P27" s="158">
+      <c r="P27" s="156">
         <v>15000</v>
       </c>
-      <c r="Q27" s="158">
+      <c r="Q27" s="156">
         <v>585000</v>
       </c>
-      <c r="R27" s="158">
+      <c r="R27" s="156">
         <v>830000</v>
       </c>
-      <c r="S27" s="156">
+      <c r="S27" s="154">
         <f>R27-Q27</f>
         <v>245000</v>
       </c>
@@ -4426,13 +4445,13 @@
     <row r="28" spans="1:41" s="5" customFormat="1" ht="49.5">
       <c r="A28" s="4"/>
       <c r="B28" s="44" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C28" s="44" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D28" s="42" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="E28" s="111">
         <v>46134</v>
@@ -4453,31 +4472,31 @@
         <f t="shared" si="4"/>
         <v>840000</v>
       </c>
-      <c r="K28" s="157">
+      <c r="K28" s="155">
         <v>1</v>
       </c>
-      <c r="L28" s="158">
+      <c r="L28" s="156">
         <v>60000</v>
       </c>
-      <c r="M28" s="158">
+      <c r="M28" s="156">
         <v>60000</v>
       </c>
-      <c r="N28" s="158">
+      <c r="N28" s="156">
         <v>0</v>
       </c>
-      <c r="O28" s="158">
+      <c r="O28" s="156">
         <v>20000</v>
       </c>
-      <c r="P28" s="158">
+      <c r="P28" s="156">
         <v>15000</v>
       </c>
-      <c r="Q28" s="158">
+      <c r="Q28" s="156">
         <v>115000</v>
       </c>
-      <c r="R28" s="158">
+      <c r="R28" s="156">
         <v>98000</v>
       </c>
-      <c r="S28" s="156">
+      <c r="S28" s="154">
         <f>R28-Q28</f>
         <v>-17000</v>
       </c>
@@ -4507,13 +4526,13 @@
     <row r="29" spans="1:41" s="5" customFormat="1" ht="30" customHeight="1">
       <c r="A29" s="4"/>
       <c r="B29" s="44" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C29" s="44" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D29" s="42" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E29" s="111">
         <v>46135</v>
@@ -4522,7 +4541,7 @@
         <v>46141</v>
       </c>
       <c r="G29" s="111">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="H29" s="52">
         <v>10</v>
@@ -4534,31 +4553,31 @@
         <f>H29*I29</f>
         <v>350000</v>
       </c>
-      <c r="K29" s="157">
+      <c r="K29" s="155">
         <v>1</v>
       </c>
-      <c r="L29" s="158">
+      <c r="L29" s="156">
         <v>30000</v>
       </c>
-      <c r="M29" s="158">
+      <c r="M29" s="156">
         <v>30000</v>
       </c>
-      <c r="N29" s="158">
+      <c r="N29" s="156">
         <v>0</v>
       </c>
-      <c r="O29" s="158">
+      <c r="O29" s="156">
         <v>15000</v>
       </c>
-      <c r="P29" s="158">
+      <c r="P29" s="156">
         <v>10000</v>
       </c>
-      <c r="Q29" s="158">
+      <c r="Q29" s="156">
         <v>550000</v>
       </c>
-      <c r="R29" s="158">
+      <c r="R29" s="156">
         <v>520000</v>
       </c>
-      <c r="S29" s="156">
+      <c r="S29" s="154">
         <f>R29-Q29</f>
         <v>-30000</v>
       </c>
@@ -4588,13 +4607,13 @@
     <row r="30" spans="1:41" s="5" customFormat="1" ht="30" customHeight="1">
       <c r="A30" s="4"/>
       <c r="B30" s="44" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C30" s="44" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D30" s="42" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="E30" s="111">
         <v>46135</v>
@@ -4615,31 +4634,31 @@
         <f>H30*I30</f>
         <v>420000</v>
       </c>
-      <c r="K30" s="157">
+      <c r="K30" s="155">
         <v>1</v>
       </c>
-      <c r="L30" s="158">
+      <c r="L30" s="156">
         <v>30000</v>
       </c>
-      <c r="M30" s="158">
+      <c r="M30" s="156">
         <v>30000</v>
       </c>
-      <c r="N30" s="158">
+      <c r="N30" s="156">
         <v>0</v>
       </c>
-      <c r="O30" s="158">
+      <c r="O30" s="156">
         <v>15000</v>
       </c>
-      <c r="P30" s="158">
+      <c r="P30" s="156">
         <v>10000</v>
       </c>
-      <c r="Q30" s="158">
+      <c r="Q30" s="156">
         <v>650000</v>
       </c>
-      <c r="R30" s="158">
+      <c r="R30" s="156">
         <v>580000</v>
       </c>
-      <c r="S30" s="156">
+      <c r="S30" s="154">
         <f>R30-Q30</f>
         <v>-70000</v>
       </c>
@@ -4669,13 +4688,13 @@
     <row r="31" spans="1:41" s="5" customFormat="1" ht="106.5" customHeight="1">
       <c r="A31" s="4"/>
       <c r="B31" s="44" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C31" s="44" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D31" s="42" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="E31" s="111">
         <v>46137</v>
@@ -4687,40 +4706,40 @@
         <v>46148</v>
       </c>
       <c r="H31" s="52">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I31" s="75">
         <v>35000</v>
       </c>
       <c r="J31" s="43">
         <f>H31*I31</f>
-        <v>350000</v>
-      </c>
-      <c r="K31" s="157">
+        <v>175000</v>
+      </c>
+      <c r="K31" s="155">
         <v>1</v>
       </c>
-      <c r="L31" s="158">
+      <c r="L31" s="156">
         <v>40000</v>
       </c>
-      <c r="M31" s="158">
+      <c r="M31" s="156">
         <v>40000</v>
       </c>
-      <c r="N31" s="158">
+      <c r="N31" s="156">
         <v>0</v>
       </c>
-      <c r="O31" s="158">
+      <c r="O31" s="156">
         <v>15000</v>
       </c>
-      <c r="P31" s="158">
+      <c r="P31" s="156">
         <v>10000</v>
       </c>
-      <c r="Q31" s="158">
+      <c r="Q31" s="156">
         <v>650000</v>
       </c>
-      <c r="R31" s="158">
+      <c r="R31" s="156">
         <v>770000</v>
       </c>
-      <c r="S31" s="156">
+      <c r="S31" s="154">
         <f>R31-Q31</f>
         <v>120000</v>
       </c>
@@ -4749,13 +4768,13 @@
     </row>
     <row r="32" spans="1:41" s="1" customFormat="1" ht="33" customHeight="1">
       <c r="B32" s="44" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C32" s="44" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D32" s="44" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E32" s="111">
         <v>46138</v>
@@ -4767,40 +4786,40 @@
         <v>46149</v>
       </c>
       <c r="H32" s="52">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I32" s="75">
         <v>35000</v>
       </c>
       <c r="J32" s="43">
         <f>H32*I32</f>
-        <v>280000</v>
-      </c>
-      <c r="K32" s="157">
+        <v>560000</v>
+      </c>
+      <c r="K32" s="155">
         <v>1</v>
       </c>
-      <c r="L32" s="158">
+      <c r="L32" s="156">
         <v>40000</v>
       </c>
-      <c r="M32" s="158">
+      <c r="M32" s="156">
         <v>40000</v>
       </c>
-      <c r="N32" s="158">
+      <c r="N32" s="156">
         <v>0</v>
       </c>
-      <c r="O32" s="158">
+      <c r="O32" s="156">
         <v>15000</v>
       </c>
-      <c r="P32" s="158">
+      <c r="P32" s="156">
         <v>10000</v>
       </c>
-      <c r="Q32" s="158">
+      <c r="Q32" s="156">
         <v>750000</v>
       </c>
-      <c r="R32" s="158">
+      <c r="R32" s="156">
         <v>620000</v>
       </c>
-      <c r="S32" s="156">
+      <c r="S32" s="154">
         <f>R32-Q32</f>
         <v>-130000</v>
       </c>
@@ -4808,13 +4827,13 @@
     <row r="33" spans="1:41" ht="49.5">
       <c r="A33" s="1"/>
       <c r="B33" s="44" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C33" s="44" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D33" s="44" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E33" s="111">
         <v>46139</v>
@@ -4826,40 +4845,40 @@
         <v>46150</v>
       </c>
       <c r="H33" s="52">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I33" s="75">
         <v>35000</v>
       </c>
       <c r="J33" s="43">
         <f>H33*I33</f>
-        <v>350000</v>
-      </c>
-      <c r="K33" s="157">
+        <v>700000</v>
+      </c>
+      <c r="K33" s="155">
         <v>1</v>
       </c>
-      <c r="L33" s="158">
+      <c r="L33" s="156">
         <v>25000</v>
       </c>
-      <c r="M33" s="158">
+      <c r="M33" s="156">
         <v>25000</v>
       </c>
-      <c r="N33" s="158">
+      <c r="N33" s="156">
         <v>0</v>
       </c>
-      <c r="O33" s="158">
+      <c r="O33" s="156">
         <v>15000</v>
       </c>
-      <c r="P33" s="158">
+      <c r="P33" s="156">
         <v>10000</v>
       </c>
-      <c r="Q33" s="158">
+      <c r="Q33" s="156">
         <v>500000</v>
       </c>
-      <c r="R33" s="158">
+      <c r="R33" s="156">
         <v>480000</v>
       </c>
-      <c r="S33" s="156">
+      <c r="S33" s="154">
         <f>R33-Q33</f>
         <v>-20000</v>
       </c>
@@ -4889,13 +4908,13 @@
     <row r="34" spans="1:41" ht="64.5" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="82" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C34" s="44" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D34" s="44" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="E34" s="111">
         <v>46140</v>
@@ -4907,40 +4926,40 @@
         <v>46152</v>
       </c>
       <c r="H34" s="52">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I34" s="75">
         <v>35000</v>
       </c>
       <c r="J34" s="43">
         <f>H34*I34</f>
-        <v>350000</v>
-      </c>
-      <c r="K34" s="157">
+        <v>560000</v>
+      </c>
+      <c r="K34" s="155">
         <v>1</v>
       </c>
-      <c r="L34" s="158">
+      <c r="L34" s="156">
         <v>25000</v>
       </c>
-      <c r="M34" s="158">
+      <c r="M34" s="156">
         <v>25000</v>
       </c>
-      <c r="N34" s="158">
+      <c r="N34" s="156">
         <v>0</v>
       </c>
-      <c r="O34" s="158">
+      <c r="O34" s="156">
         <v>15000</v>
       </c>
-      <c r="P34" s="158">
+      <c r="P34" s="156">
         <v>10000</v>
       </c>
-      <c r="Q34" s="158">
+      <c r="Q34" s="156">
         <v>580000</v>
       </c>
-      <c r="R34" s="158">
+      <c r="R34" s="156">
         <v>520000</v>
       </c>
-      <c r="S34" s="156">
+      <c r="S34" s="154">
         <f>R34-Q34</f>
         <v>-60000</v>
       </c>
@@ -4970,13 +4989,13 @@
     <row r="35" spans="1:41" ht="36.75">
       <c r="A35" s="1"/>
       <c r="B35" s="44" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C35" s="44" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D35" s="44" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="E35" s="111">
         <v>46141</v>
@@ -4988,40 +5007,40 @@
         <v>46154</v>
       </c>
       <c r="H35" s="52">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I35" s="75">
         <v>35000</v>
       </c>
       <c r="J35" s="43">
         <f>H35*I35</f>
-        <v>210000</v>
-      </c>
-      <c r="K35" s="157">
+        <v>455000</v>
+      </c>
+      <c r="K35" s="155">
         <v>1</v>
       </c>
-      <c r="L35" s="158">
+      <c r="L35" s="156">
         <v>30000</v>
       </c>
-      <c r="M35" s="158">
+      <c r="M35" s="156">
         <v>30000</v>
       </c>
-      <c r="N35" s="158">
+      <c r="N35" s="156">
         <v>0</v>
       </c>
-      <c r="O35" s="158">
+      <c r="O35" s="156">
         <v>15000</v>
       </c>
-      <c r="P35" s="158">
+      <c r="P35" s="156">
         <v>10000</v>
       </c>
-      <c r="Q35" s="158">
+      <c r="Q35" s="156">
         <v>600000</v>
       </c>
-      <c r="R35" s="158">
+      <c r="R35" s="156">
         <v>570000</v>
       </c>
-      <c r="S35" s="156">
+      <c r="S35" s="154">
         <f>R35-Q35</f>
         <v>-30000</v>
       </c>
@@ -5051,13 +5070,13 @@
     <row r="36" spans="1:41" ht="24.75">
       <c r="A36" s="1"/>
       <c r="B36" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="D36" s="44" t="s">
         <v>80</v>
-      </c>
-      <c r="C36" s="44" t="s">
-        <v>81</v>
-      </c>
-      <c r="D36" s="44" t="s">
-        <v>29</v>
       </c>
       <c r="E36" s="111">
         <v>46143</v>
@@ -5069,40 +5088,40 @@
         <v>46156</v>
       </c>
       <c r="H36" s="52">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I36" s="75">
         <v>35000</v>
       </c>
       <c r="J36" s="43">
         <f>H36*I36</f>
-        <v>210000</v>
-      </c>
-      <c r="K36" s="157">
+        <v>385000</v>
+      </c>
+      <c r="K36" s="155">
         <v>1</v>
       </c>
-      <c r="L36" s="158">
+      <c r="L36" s="156">
         <v>20000</v>
       </c>
-      <c r="M36" s="158">
+      <c r="M36" s="156">
         <v>20000</v>
       </c>
-      <c r="N36" s="158">
+      <c r="N36" s="156">
         <v>0</v>
       </c>
-      <c r="O36" s="158">
+      <c r="O36" s="156">
         <v>15000</v>
       </c>
-      <c r="P36" s="158">
+      <c r="P36" s="156">
         <v>10000</v>
       </c>
-      <c r="Q36" s="158">
+      <c r="Q36" s="156">
         <v>500000</v>
       </c>
-      <c r="R36" s="158">
+      <c r="R36" s="156">
         <v>430000</v>
       </c>
-      <c r="S36" s="156">
+      <c r="S36" s="154">
         <f>R36-Q36</f>
         <v>-70000</v>
       </c>
@@ -5132,13 +5151,13 @@
     <row r="37" spans="1:41" ht="36.75">
       <c r="A37" s="1"/>
       <c r="B37" s="44" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C37" s="44" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D37" s="44" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="E37" s="111">
         <v>46144</v>
@@ -5150,40 +5169,40 @@
         <v>46158</v>
       </c>
       <c r="H37" s="52">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I37" s="75">
         <v>35000</v>
       </c>
       <c r="J37" s="43">
         <f>H37*I37</f>
-        <v>210000</v>
-      </c>
-      <c r="K37" s="157">
+        <v>315000</v>
+      </c>
+      <c r="K37" s="155">
         <v>1</v>
       </c>
-      <c r="L37" s="158">
+      <c r="L37" s="156">
         <v>40000</v>
       </c>
-      <c r="M37" s="158">
+      <c r="M37" s="156">
         <v>40000</v>
       </c>
-      <c r="N37" s="158">
+      <c r="N37" s="156">
         <v>0</v>
       </c>
-      <c r="O37" s="158">
+      <c r="O37" s="156">
         <v>20000</v>
       </c>
-      <c r="P37" s="158">
+      <c r="P37" s="156">
         <v>10000</v>
       </c>
-      <c r="Q37" s="158">
+      <c r="Q37" s="156">
         <v>800000</v>
       </c>
-      <c r="R37" s="158">
+      <c r="R37" s="156">
         <v>720000</v>
       </c>
-      <c r="S37" s="156">
+      <c r="S37" s="154">
         <f>R37-Q37</f>
         <v>-80000</v>
       </c>
@@ -5213,7 +5232,7 @@
     <row r="38" spans="1:41" ht="18">
       <c r="A38" s="1"/>
       <c r="B38" s="35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C38" s="35"/>
       <c r="D38" s="45"/>
@@ -5222,7 +5241,7 @@
       <c r="G38" s="46"/>
       <c r="H38" s="76">
         <f>SUM(H22:H37)</f>
-        <v>176</v>
+        <v>214</v>
       </c>
       <c r="I38" s="77">
         <f>SUM(I22:I37)</f>
@@ -5230,34 +5249,34 @@
       </c>
       <c r="J38" s="47">
         <f>SUM(J22:J37)</f>
-        <v>6160000</v>
-      </c>
-      <c r="K38" s="154"/>
-      <c r="L38" s="158">
+        <v>7490000</v>
+      </c>
+      <c r="K38" s="152"/>
+      <c r="L38" s="156">
         <f>SUM(L21:L37)</f>
         <v>610000</v>
       </c>
-      <c r="M38" s="158">
+      <c r="M38" s="156">
         <f>SUM(M21:M37)</f>
         <v>610000</v>
       </c>
-      <c r="N38" s="158">
+      <c r="N38" s="156">
         <f>SUM(N21:N37)</f>
         <v>0</v>
       </c>
-      <c r="O38" s="158">
+      <c r="O38" s="156">
         <f>SUM(O21:O37)</f>
         <v>265000</v>
       </c>
-      <c r="P38" s="158">
+      <c r="P38" s="156">
         <f>SUM(P21:P37)</f>
         <v>185000</v>
       </c>
-      <c r="Q38" s="158">
+      <c r="Q38" s="156">
         <f>SUM(Q21:Q37)</f>
         <v>10360000</v>
       </c>
-      <c r="R38" s="158">
+      <c r="R38" s="156">
         <f>SUM(R21:R37)</f>
         <v>9898000</v>
       </c>
@@ -5288,8 +5307,26 @@
       <c r="AN38" s="1"/>
       <c r="AO38" s="1"/>
     </row>
-    <row r="39" spans="1:41">
+    <row r="39" spans="1:41" ht="18">
       <c r="A39" s="1"/>
+      <c r="B39" s="173"/>
+      <c r="C39" s="173"/>
+      <c r="D39" s="174"/>
+      <c r="E39" s="175"/>
+      <c r="F39" s="175"/>
+      <c r="G39" s="175"/>
+      <c r="H39" s="176"/>
+      <c r="I39" s="177"/>
+      <c r="J39" s="178"/>
+      <c r="K39" s="179"/>
+      <c r="L39" s="180"/>
+      <c r="M39" s="180"/>
+      <c r="N39" s="180"/>
+      <c r="O39" s="180"/>
+      <c r="P39" s="180"/>
+      <c r="Q39" s="180"/>
+      <c r="R39" s="180"/>
+      <c r="S39" s="181"/>
       <c r="T39" s="1"/>
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
@@ -5313,8 +5350,14 @@
       <c r="AN39" s="1"/>
       <c r="AO39" s="1"/>
     </row>
-    <row r="40" spans="1:41" ht="13.5" customHeight="1">
+    <row r="40" spans="1:41">
       <c r="A40" s="1"/>
+      <c r="T40" s="1"/>
+      <c r="U40" s="1"/>
+      <c r="V40" s="1"/>
+      <c r="W40" s="1"/>
+      <c r="X40" s="1"/>
+      <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
       <c r="AB40" s="1"/>
@@ -5332,14 +5375,8 @@
       <c r="AN40" s="1"/>
       <c r="AO40" s="1"/>
     </row>
-    <row r="41" spans="1:41">
+    <row r="41" spans="1:41" ht="13.5" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="T41" s="1"/>
-      <c r="U41" s="1"/>
-      <c r="V41" s="1"/>
-      <c r="W41" s="1"/>
-      <c r="X41" s="1"/>
-      <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
       <c r="AA41" s="1"/>
       <c r="AB41" s="1"/>
@@ -5659,24 +5696,6 @@
     </row>
     <row r="54" spans="1:41">
       <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="80"/>
-      <c r="I54" s="81"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
-      <c r="M54" s="56"/>
-      <c r="N54" s="56"/>
-      <c r="O54" s="56"/>
-      <c r="P54" s="56"/>
-      <c r="Q54" s="56"/>
-      <c r="R54" s="56"/>
-      <c r="S54" s="1"/>
       <c r="T54" s="1"/>
       <c r="U54" s="1"/>
       <c r="V54" s="1"/>
@@ -6023,6 +6042,26 @@
       <c r="S62" s="1"/>
       <c r="T62" s="1"/>
       <c r="U62" s="1"/>
+      <c r="V62" s="1"/>
+      <c r="W62" s="1"/>
+      <c r="X62" s="1"/>
+      <c r="Y62" s="1"/>
+      <c r="Z62" s="1"/>
+      <c r="AA62" s="1"/>
+      <c r="AB62" s="1"/>
+      <c r="AC62" s="1"/>
+      <c r="AD62" s="1"/>
+      <c r="AE62" s="1"/>
+      <c r="AF62" s="1"/>
+      <c r="AG62" s="1"/>
+      <c r="AH62" s="1"/>
+      <c r="AI62" s="1"/>
+      <c r="AJ62" s="1"/>
+      <c r="AK62" s="1"/>
+      <c r="AL62" s="1"/>
+      <c r="AM62" s="1"/>
+      <c r="AN62" s="1"/>
+      <c r="AO62" s="1"/>
     </row>
     <row r="63" spans="1:41">
       <c r="A63" s="1"/>
@@ -6438,7 +6477,7 @@
       <c r="T80" s="1"/>
       <c r="U80" s="1"/>
     </row>
-    <row r="81" spans="1:21">
+    <row r="81" spans="1:21" ht="13.5" customHeight="1">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -6461,7 +6500,7 @@
       <c r="T81" s="1"/>
       <c r="U81" s="1"/>
     </row>
-    <row r="82" spans="1:21">
+    <row r="82" spans="1:21" ht="13.5" customHeight="1">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -6484,7 +6523,7 @@
       <c r="T82" s="1"/>
       <c r="U82" s="1"/>
     </row>
-    <row r="83" spans="1:21">
+    <row r="83" spans="1:21" ht="13.5" customHeight="1">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -6507,7 +6546,7 @@
       <c r="T83" s="1"/>
       <c r="U83" s="1"/>
     </row>
-    <row r="84" spans="1:21">
+    <row r="84" spans="1:21" ht="13.5" customHeight="1">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -6530,7 +6569,7 @@
       <c r="T84" s="1"/>
       <c r="U84" s="1"/>
     </row>
-    <row r="85" spans="1:21">
+    <row r="85" spans="1:21" ht="13.5" customHeight="1">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -6553,7 +6592,7 @@
       <c r="T85" s="1"/>
       <c r="U85" s="1"/>
     </row>
-    <row r="86" spans="1:21">
+    <row r="86" spans="1:21" ht="13.5" customHeight="1">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -6576,7 +6615,7 @@
       <c r="T86" s="1"/>
       <c r="U86" s="1"/>
     </row>
-    <row r="87" spans="1:21">
+    <row r="87" spans="1:21" ht="13.5" customHeight="1">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -6599,7 +6638,7 @@
       <c r="T87" s="1"/>
       <c r="U87" s="1"/>
     </row>
-    <row r="88" spans="1:21">
+    <row r="88" spans="1:21" ht="13.5" customHeight="1">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -6622,7 +6661,7 @@
       <c r="T88" s="1"/>
       <c r="U88" s="1"/>
     </row>
-    <row r="89" spans="1:21">
+    <row r="89" spans="1:21" ht="13.5" customHeight="1">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -6645,7 +6684,7 @@
       <c r="T89" s="1"/>
       <c r="U89" s="1"/>
     </row>
-    <row r="90" spans="1:21">
+    <row r="90" spans="1:21" ht="13.5" customHeight="1">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -6668,7 +6707,7 @@
       <c r="T90" s="1"/>
       <c r="U90" s="1"/>
     </row>
-    <row r="91" spans="1:21">
+    <row r="91" spans="1:21" ht="13.5" customHeight="1">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -6691,7 +6730,7 @@
       <c r="T91" s="1"/>
       <c r="U91" s="1"/>
     </row>
-    <row r="92" spans="1:21">
+    <row r="92" spans="1:21" ht="13.5" customHeight="1">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -6714,7 +6753,7 @@
       <c r="T92" s="1"/>
       <c r="U92" s="1"/>
     </row>
-    <row r="93" spans="1:21">
+    <row r="93" spans="1:21" ht="13.5" customHeight="1">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -6737,7 +6776,7 @@
       <c r="T93" s="1"/>
       <c r="U93" s="1"/>
     </row>
-    <row r="94" spans="1:21">
+    <row r="94" spans="1:21" ht="13.5" customHeight="1">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -6760,7 +6799,7 @@
       <c r="T94" s="1"/>
       <c r="U94" s="1"/>
     </row>
-    <row r="95" spans="1:21">
+    <row r="95" spans="1:21" ht="13.5" customHeight="1">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -6783,7 +6822,7 @@
       <c r="T95" s="1"/>
       <c r="U95" s="1"/>
     </row>
-    <row r="96" spans="1:21">
+    <row r="96" spans="1:21" ht="13.5" customHeight="1">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -6806,7 +6845,7 @@
       <c r="T96" s="1"/>
       <c r="U96" s="1"/>
     </row>
-    <row r="97" spans="1:21">
+    <row r="97" spans="1:21" ht="13.5" customHeight="1">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -6829,7 +6868,7 @@
       <c r="T97" s="1"/>
       <c r="U97" s="1"/>
     </row>
-    <row r="98" spans="1:21">
+    <row r="98" spans="1:21" ht="13.5" customHeight="1">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -6852,7 +6891,7 @@
       <c r="T98" s="1"/>
       <c r="U98" s="1"/>
     </row>
-    <row r="99" spans="1:21">
+    <row r="99" spans="1:21" ht="13.5" customHeight="1">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -6875,7 +6914,7 @@
       <c r="T99" s="1"/>
       <c r="U99" s="1"/>
     </row>
-    <row r="100" spans="1:21">
+    <row r="100" spans="1:21" ht="13.5" customHeight="1">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -6898,7 +6937,7 @@
       <c r="T100" s="1"/>
       <c r="U100" s="1"/>
     </row>
-    <row r="101" spans="1:21">
+    <row r="101" spans="1:21" ht="13.5" customHeight="1">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -6921,7 +6960,7 @@
       <c r="T101" s="1"/>
       <c r="U101" s="1"/>
     </row>
-    <row r="102" spans="1:21">
+    <row r="102" spans="1:21" ht="13.5" customHeight="1">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -6944,7 +6983,7 @@
       <c r="T102" s="1"/>
       <c r="U102" s="1"/>
     </row>
-    <row r="103" spans="1:21">
+    <row r="103" spans="1:21" ht="13.5" customHeight="1">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -6967,7 +7006,7 @@
       <c r="T103" s="1"/>
       <c r="U103" s="1"/>
     </row>
-    <row r="104" spans="1:21">
+    <row r="104" spans="1:21" ht="13.5" customHeight="1">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -6990,7 +7029,7 @@
       <c r="T104" s="1"/>
       <c r="U104" s="1"/>
     </row>
-    <row r="105" spans="1:21">
+    <row r="105" spans="1:21" ht="13.5" customHeight="1">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -7013,7 +7052,7 @@
       <c r="T105" s="1"/>
       <c r="U105" s="1"/>
     </row>
-    <row r="106" spans="1:21">
+    <row r="106" spans="1:21" ht="13.5" customHeight="1">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -7036,7 +7075,7 @@
       <c r="T106" s="1"/>
       <c r="U106" s="1"/>
     </row>
-    <row r="107" spans="1:21">
+    <row r="107" spans="1:21" ht="13.5" customHeight="1">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -7059,7 +7098,7 @@
       <c r="T107" s="1"/>
       <c r="U107" s="1"/>
     </row>
-    <row r="108" spans="1:21">
+    <row r="108" spans="1:21" ht="13.5" customHeight="1">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -7082,7 +7121,7 @@
       <c r="T108" s="1"/>
       <c r="U108" s="1"/>
     </row>
-    <row r="109" spans="1:21">
+    <row r="109" spans="1:21" ht="13.5" customHeight="1">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -7105,7 +7144,7 @@
       <c r="T109" s="1"/>
       <c r="U109" s="1"/>
     </row>
-    <row r="110" spans="1:21">
+    <row r="110" spans="1:21" ht="13.5" customHeight="1">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -7128,7 +7167,7 @@
       <c r="T110" s="1"/>
       <c r="U110" s="1"/>
     </row>
-    <row r="111" spans="1:21">
+    <row r="111" spans="1:21" ht="13.5" customHeight="1">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -7151,7 +7190,7 @@
       <c r="T111" s="1"/>
       <c r="U111" s="1"/>
     </row>
-    <row r="112" spans="1:21">
+    <row r="112" spans="1:21" ht="13.5" customHeight="1">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -7174,7 +7213,7 @@
       <c r="T112" s="1"/>
       <c r="U112" s="1"/>
     </row>
-    <row r="113" spans="1:21">
+    <row r="113" spans="1:21" ht="13.5" customHeight="1">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -7197,7 +7236,7 @@
       <c r="T113" s="1"/>
       <c r="U113" s="1"/>
     </row>
-    <row r="114" spans="1:21">
+    <row r="114" spans="1:21" ht="13.5" customHeight="1">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -7220,7 +7259,7 @@
       <c r="T114" s="1"/>
       <c r="U114" s="1"/>
     </row>
-    <row r="115" spans="1:21">
+    <row r="115" spans="1:21" ht="13.5" customHeight="1">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -7243,7 +7282,7 @@
       <c r="T115" s="1"/>
       <c r="U115" s="1"/>
     </row>
-    <row r="116" spans="1:21">
+    <row r="116" spans="1:21" ht="13.5" customHeight="1">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -7266,7 +7305,7 @@
       <c r="T116" s="1"/>
       <c r="U116" s="1"/>
     </row>
-    <row r="117" spans="1:21">
+    <row r="117" spans="1:21" ht="13.5" customHeight="1">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -7289,7 +7328,7 @@
       <c r="T117" s="1"/>
       <c r="U117" s="1"/>
     </row>
-    <row r="118" spans="1:21">
+    <row r="118" spans="1:21" ht="13.5" customHeight="1">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -7312,7 +7351,7 @@
       <c r="T118" s="1"/>
       <c r="U118" s="1"/>
     </row>
-    <row r="119" spans="1:21">
+    <row r="119" spans="1:21" ht="13.5" customHeight="1">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -7335,7 +7374,7 @@
       <c r="T119" s="1"/>
       <c r="U119" s="1"/>
     </row>
-    <row r="120" spans="1:21">
+    <row r="120" spans="1:21" ht="13.5" customHeight="1">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -7358,7 +7397,7 @@
       <c r="T120" s="1"/>
       <c r="U120" s="1"/>
     </row>
-    <row r="121" spans="1:21">
+    <row r="121" spans="1:21" ht="13.5" customHeight="1">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -7381,7 +7420,7 @@
       <c r="T121" s="1"/>
       <c r="U121" s="1"/>
     </row>
-    <row r="122" spans="1:21">
+    <row r="122" spans="1:21" ht="13.5" customHeight="1">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -7404,7 +7443,7 @@
       <c r="T122" s="1"/>
       <c r="U122" s="1"/>
     </row>
-    <row r="123" spans="1:21">
+    <row r="123" spans="1:21" ht="13.5" customHeight="1">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -7427,7 +7466,7 @@
       <c r="T123" s="1"/>
       <c r="U123" s="1"/>
     </row>
-    <row r="124" spans="1:21">
+    <row r="124" spans="1:21" ht="13.5" customHeight="1">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -7450,7 +7489,7 @@
       <c r="T124" s="1"/>
       <c r="U124" s="1"/>
     </row>
-    <row r="125" spans="1:21">
+    <row r="125" spans="1:21" ht="13.5" customHeight="1">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -7473,7 +7512,7 @@
       <c r="T125" s="1"/>
       <c r="U125" s="1"/>
     </row>
-    <row r="126" spans="1:21">
+    <row r="126" spans="1:21" ht="13.5" customHeight="1">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -7496,7 +7535,7 @@
       <c r="T126" s="1"/>
       <c r="U126" s="1"/>
     </row>
-    <row r="127" spans="1:21">
+    <row r="127" spans="1:21" ht="13.5" customHeight="1">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -7519,7 +7558,7 @@
       <c r="T127" s="1"/>
       <c r="U127" s="1"/>
     </row>
-    <row r="128" spans="1:21">
+    <row r="128" spans="1:21" ht="13.5" customHeight="1">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -7542,7 +7581,7 @@
       <c r="T128" s="1"/>
       <c r="U128" s="1"/>
     </row>
-    <row r="129" spans="1:21">
+    <row r="129" spans="1:21" ht="13.5" customHeight="1">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -7565,7 +7604,7 @@
       <c r="T129" s="1"/>
       <c r="U129" s="1"/>
     </row>
-    <row r="130" spans="1:21">
+    <row r="130" spans="1:21" ht="13.5" customHeight="1">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -7588,7 +7627,7 @@
       <c r="T130" s="1"/>
       <c r="U130" s="1"/>
     </row>
-    <row r="131" spans="1:21">
+    <row r="131" spans="1:21" ht="13.5" customHeight="1">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -7611,7 +7650,7 @@
       <c r="T131" s="1"/>
       <c r="U131" s="1"/>
     </row>
-    <row r="132" spans="1:21">
+    <row r="132" spans="1:21" ht="13.5" customHeight="1">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -7634,7 +7673,7 @@
       <c r="T132" s="1"/>
       <c r="U132" s="1"/>
     </row>
-    <row r="133" spans="1:21">
+    <row r="133" spans="1:21" ht="13.5" customHeight="1">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -7657,7 +7696,7 @@
       <c r="T133" s="1"/>
       <c r="U133" s="1"/>
     </row>
-    <row r="134" spans="1:21">
+    <row r="134" spans="1:21" ht="13.5" customHeight="1">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -7680,7 +7719,7 @@
       <c r="T134" s="1"/>
       <c r="U134" s="1"/>
     </row>
-    <row r="135" spans="1:21">
+    <row r="135" spans="1:21" ht="13.5" customHeight="1">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -7703,7 +7742,7 @@
       <c r="T135" s="1"/>
       <c r="U135" s="1"/>
     </row>
-    <row r="136" spans="1:21">
+    <row r="136" spans="1:21" ht="13.5" customHeight="1">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -7726,7 +7765,7 @@
       <c r="T136" s="1"/>
       <c r="U136" s="1"/>
     </row>
-    <row r="137" spans="1:21">
+    <row r="137" spans="1:21" ht="13.5" customHeight="1">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -7749,7 +7788,7 @@
       <c r="T137" s="1"/>
       <c r="U137" s="1"/>
     </row>
-    <row r="138" spans="1:21">
+    <row r="138" spans="1:21" ht="13.5" customHeight="1">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -7772,7 +7811,7 @@
       <c r="T138" s="1"/>
       <c r="U138" s="1"/>
     </row>
-    <row r="139" spans="1:21">
+    <row r="139" spans="1:21" ht="13.5" customHeight="1">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -7795,7 +7834,7 @@
       <c r="T139" s="1"/>
       <c r="U139" s="1"/>
     </row>
-    <row r="140" spans="1:21">
+    <row r="140" spans="1:21" ht="13.5" customHeight="1">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -7818,7 +7857,7 @@
       <c r="T140" s="1"/>
       <c r="U140" s="1"/>
     </row>
-    <row r="141" spans="1:21">
+    <row r="141" spans="1:21" ht="13.5" customHeight="1">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -7841,7 +7880,7 @@
       <c r="T141" s="1"/>
       <c r="U141" s="1"/>
     </row>
-    <row r="142" spans="1:21">
+    <row r="142" spans="1:21" ht="13.5" customHeight="1">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -7864,7 +7903,7 @@
       <c r="T142" s="1"/>
       <c r="U142" s="1"/>
     </row>
-    <row r="143" spans="1:21">
+    <row r="143" spans="1:21" ht="13.5" customHeight="1">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -7887,7 +7926,7 @@
       <c r="T143" s="1"/>
       <c r="U143" s="1"/>
     </row>
-    <row r="144" spans="1:21">
+    <row r="144" spans="1:21" ht="13.5" customHeight="1">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -7910,7 +7949,7 @@
       <c r="T144" s="1"/>
       <c r="U144" s="1"/>
     </row>
-    <row r="145" spans="1:21">
+    <row r="145" spans="1:21" ht="13.5" customHeight="1">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -7933,7 +7972,7 @@
       <c r="T145" s="1"/>
       <c r="U145" s="1"/>
     </row>
-    <row r="146" spans="1:21">
+    <row r="146" spans="1:21" ht="13.5" customHeight="1">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -7956,7 +7995,7 @@
       <c r="T146" s="1"/>
       <c r="U146" s="1"/>
     </row>
-    <row r="147" spans="1:21">
+    <row r="147" spans="1:21" ht="13.5" customHeight="1">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -7979,7 +8018,7 @@
       <c r="T147" s="1"/>
       <c r="U147" s="1"/>
     </row>
-    <row r="148" spans="1:21">
+    <row r="148" spans="1:21" ht="13.5" customHeight="1">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -8002,7 +8041,7 @@
       <c r="T148" s="1"/>
       <c r="U148" s="1"/>
     </row>
-    <row r="149" spans="1:21">
+    <row r="149" spans="1:21" ht="13.5" customHeight="1">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -8025,7 +8064,7 @@
       <c r="T149" s="1"/>
       <c r="U149" s="1"/>
     </row>
-    <row r="150" spans="1:21">
+    <row r="150" spans="1:21" ht="13.5" customHeight="1">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -8048,7 +8087,7 @@
       <c r="T150" s="1"/>
       <c r="U150" s="1"/>
     </row>
-    <row r="151" spans="1:21">
+    <row r="151" spans="1:21" ht="13.5" customHeight="1">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -8071,7 +8110,7 @@
       <c r="T151" s="1"/>
       <c r="U151" s="1"/>
     </row>
-    <row r="152" spans="1:21">
+    <row r="152" spans="1:21" ht="13.5" customHeight="1">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -8094,7 +8133,7 @@
       <c r="T152" s="1"/>
       <c r="U152" s="1"/>
     </row>
-    <row r="153" spans="1:21">
+    <row r="153" spans="1:21" ht="13.5" customHeight="1">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -8117,7 +8156,7 @@
       <c r="T153" s="1"/>
       <c r="U153" s="1"/>
     </row>
-    <row r="154" spans="1:21">
+    <row r="154" spans="1:21" ht="13.5" customHeight="1">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -8140,7 +8179,7 @@
       <c r="T154" s="1"/>
       <c r="U154" s="1"/>
     </row>
-    <row r="155" spans="1:21">
+    <row r="155" spans="1:21" ht="13.5" customHeight="1">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -8163,7 +8202,7 @@
       <c r="T155" s="1"/>
       <c r="U155" s="1"/>
     </row>
-    <row r="156" spans="1:21">
+    <row r="156" spans="1:21" ht="13.5" customHeight="1">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -8186,7 +8225,7 @@
       <c r="T156" s="1"/>
       <c r="U156" s="1"/>
     </row>
-    <row r="157" spans="1:21">
+    <row r="157" spans="1:21" ht="13.5" customHeight="1">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -8209,7 +8248,7 @@
       <c r="T157" s="1"/>
       <c r="U157" s="1"/>
     </row>
-    <row r="158" spans="1:21">
+    <row r="158" spans="1:21" ht="13.5" customHeight="1">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -8232,7 +8271,7 @@
       <c r="T158" s="1"/>
       <c r="U158" s="1"/>
     </row>
-    <row r="159" spans="1:21">
+    <row r="159" spans="1:21" ht="13.5" customHeight="1">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -8255,7 +8294,7 @@
       <c r="T159" s="1"/>
       <c r="U159" s="1"/>
     </row>
-    <row r="160" spans="1:21">
+    <row r="160" spans="1:21" ht="13.5" customHeight="1">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -8278,7 +8317,7 @@
       <c r="T160" s="1"/>
       <c r="U160" s="1"/>
     </row>
-    <row r="161" spans="1:21">
+    <row r="161" spans="1:21" ht="13.5" customHeight="1">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -8301,7 +8340,7 @@
       <c r="T161" s="1"/>
       <c r="U161" s="1"/>
     </row>
-    <row r="162" spans="1:21">
+    <row r="162" spans="1:21" ht="13.5" customHeight="1">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -8324,7 +8363,7 @@
       <c r="T162" s="1"/>
       <c r="U162" s="1"/>
     </row>
-    <row r="163" spans="1:21">
+    <row r="163" spans="1:21" ht="13.5" customHeight="1">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -8347,7 +8386,7 @@
       <c r="T163" s="1"/>
       <c r="U163" s="1"/>
     </row>
-    <row r="164" spans="1:21">
+    <row r="164" spans="1:21" ht="13.5" customHeight="1">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -8370,7 +8409,7 @@
       <c r="T164" s="1"/>
       <c r="U164" s="1"/>
     </row>
-    <row r="165" spans="1:21">
+    <row r="165" spans="1:21" ht="13.5" customHeight="1">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -8393,7 +8432,7 @@
       <c r="T165" s="1"/>
       <c r="U165" s="1"/>
     </row>
-    <row r="166" spans="1:21">
+    <row r="166" spans="1:21" ht="13.5" customHeight="1">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -8416,7 +8455,7 @@
       <c r="T166" s="1"/>
       <c r="U166" s="1"/>
     </row>
-    <row r="167" spans="1:21">
+    <row r="167" spans="1:21" ht="13.5" customHeight="1">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -8439,7 +8478,7 @@
       <c r="T167" s="1"/>
       <c r="U167" s="1"/>
     </row>
-    <row r="168" spans="1:21">
+    <row r="168" spans="1:21" ht="13.5" customHeight="1">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -8462,7 +8501,7 @@
       <c r="T168" s="1"/>
       <c r="U168" s="1"/>
     </row>
-    <row r="169" spans="1:21">
+    <row r="169" spans="1:21" ht="13.5" customHeight="1">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -8485,7 +8524,7 @@
       <c r="T169" s="1"/>
       <c r="U169" s="1"/>
     </row>
-    <row r="170" spans="1:21">
+    <row r="170" spans="1:21" ht="13.5" customHeight="1">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -8508,7 +8547,7 @@
       <c r="T170" s="1"/>
       <c r="U170" s="1"/>
     </row>
-    <row r="171" spans="1:21">
+    <row r="171" spans="1:21" ht="13.5" customHeight="1">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -8531,7 +8570,7 @@
       <c r="T171" s="1"/>
       <c r="U171" s="1"/>
     </row>
-    <row r="172" spans="1:21">
+    <row r="172" spans="1:21" ht="13.5" customHeight="1">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -8554,7 +8593,7 @@
       <c r="T172" s="1"/>
       <c r="U172" s="1"/>
     </row>
-    <row r="173" spans="1:21">
+    <row r="173" spans="1:21" ht="13.5" customHeight="1">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -8577,7 +8616,7 @@
       <c r="T173" s="1"/>
       <c r="U173" s="1"/>
     </row>
-    <row r="174" spans="1:21">
+    <row r="174" spans="1:21" ht="13.5" customHeight="1">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -8600,7 +8639,7 @@
       <c r="T174" s="1"/>
       <c r="U174" s="1"/>
     </row>
-    <row r="175" spans="1:21">
+    <row r="175" spans="1:21" ht="13.5" customHeight="1">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -8623,7 +8662,7 @@
       <c r="T175" s="1"/>
       <c r="U175" s="1"/>
     </row>
-    <row r="176" spans="1:21">
+    <row r="176" spans="1:21" ht="13.5" customHeight="1">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -8646,7 +8685,7 @@
       <c r="T176" s="1"/>
       <c r="U176" s="1"/>
     </row>
-    <row r="177" spans="1:21">
+    <row r="177" spans="1:21" ht="13.5" customHeight="1">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -8669,7 +8708,7 @@
       <c r="T177" s="1"/>
       <c r="U177" s="1"/>
     </row>
-    <row r="178" spans="1:21">
+    <row r="178" spans="1:21" ht="13.5" customHeight="1">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -8692,7 +8731,7 @@
       <c r="T178" s="1"/>
       <c r="U178" s="1"/>
     </row>
-    <row r="179" spans="1:21">
+    <row r="179" spans="1:21" ht="13.5" customHeight="1">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -8715,7 +8754,7 @@
       <c r="T179" s="1"/>
       <c r="U179" s="1"/>
     </row>
-    <row r="180" spans="1:21">
+    <row r="180" spans="1:21" ht="13.5" customHeight="1">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -8738,7 +8777,7 @@
       <c r="T180" s="1"/>
       <c r="U180" s="1"/>
     </row>
-    <row r="181" spans="1:21">
+    <row r="181" spans="1:21" ht="13.5" customHeight="1">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -8761,7 +8800,7 @@
       <c r="T181" s="1"/>
       <c r="U181" s="1"/>
     </row>
-    <row r="182" spans="1:21">
+    <row r="182" spans="1:21" ht="13.5" customHeight="1">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -8784,7 +8823,7 @@
       <c r="T182" s="1"/>
       <c r="U182" s="1"/>
     </row>
-    <row r="183" spans="1:21">
+    <row r="183" spans="1:21" ht="13.5" customHeight="1">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -8807,7 +8846,7 @@
       <c r="T183" s="1"/>
       <c r="U183" s="1"/>
     </row>
-    <row r="184" spans="1:21">
+    <row r="184" spans="1:21" ht="13.5" customHeight="1">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -8830,7 +8869,7 @@
       <c r="T184" s="1"/>
       <c r="U184" s="1"/>
     </row>
-    <row r="185" spans="1:21">
+    <row r="185" spans="1:21" ht="13.5" customHeight="1">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -8853,7 +8892,7 @@
       <c r="T185" s="1"/>
       <c r="U185" s="1"/>
     </row>
-    <row r="186" spans="1:21">
+    <row r="186" spans="1:21" ht="13.5" customHeight="1">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -8876,7 +8915,7 @@
       <c r="T186" s="1"/>
       <c r="U186" s="1"/>
     </row>
-    <row r="187" spans="1:21">
+    <row r="187" spans="1:21" ht="13.5" customHeight="1">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -8899,7 +8938,7 @@
       <c r="T187" s="1"/>
       <c r="U187" s="1"/>
     </row>
-    <row r="188" spans="1:21">
+    <row r="188" spans="1:21" ht="13.5" customHeight="1">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -8922,7 +8961,7 @@
       <c r="T188" s="1"/>
       <c r="U188" s="1"/>
     </row>
-    <row r="189" spans="1:21">
+    <row r="189" spans="1:21" ht="13.5" customHeight="1">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -8945,7 +8984,7 @@
       <c r="T189" s="1"/>
       <c r="U189" s="1"/>
     </row>
-    <row r="190" spans="1:21">
+    <row r="190" spans="1:21" ht="13.5" customHeight="1">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -8968,7 +9007,7 @@
       <c r="T190" s="1"/>
       <c r="U190" s="1"/>
     </row>
-    <row r="191" spans="1:21">
+    <row r="191" spans="1:21" ht="13.5" customHeight="1">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -8991,7 +9030,7 @@
       <c r="T191" s="1"/>
       <c r="U191" s="1"/>
     </row>
-    <row r="192" spans="1:21">
+    <row r="192" spans="1:21" ht="13.5" customHeight="1">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -9014,7 +9053,7 @@
       <c r="T192" s="1"/>
       <c r="U192" s="1"/>
     </row>
-    <row r="193" spans="1:21">
+    <row r="193" spans="1:21" ht="13.5" customHeight="1">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -9037,7 +9076,7 @@
       <c r="T193" s="1"/>
       <c r="U193" s="1"/>
     </row>
-    <row r="194" spans="1:21">
+    <row r="194" spans="1:21" ht="13.5" customHeight="1">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -9060,7 +9099,7 @@
       <c r="T194" s="1"/>
       <c r="U194" s="1"/>
     </row>
-    <row r="195" spans="1:21">
+    <row r="195" spans="1:21" ht="13.5" customHeight="1">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -9083,7 +9122,7 @@
       <c r="T195" s="1"/>
       <c r="U195" s="1"/>
     </row>
-    <row r="196" spans="1:21">
+    <row r="196" spans="1:21" ht="13.5" customHeight="1">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -9106,7 +9145,7 @@
       <c r="T196" s="1"/>
       <c r="U196" s="1"/>
     </row>
-    <row r="197" spans="1:21">
+    <row r="197" spans="1:21" ht="13.5" customHeight="1">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -9129,7 +9168,7 @@
       <c r="T197" s="1"/>
       <c r="U197" s="1"/>
     </row>
-    <row r="198" spans="1:21">
+    <row r="198" spans="1:21" ht="13.5" customHeight="1">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -9152,7 +9191,7 @@
       <c r="T198" s="1"/>
       <c r="U198" s="1"/>
     </row>
-    <row r="199" spans="1:21">
+    <row r="199" spans="1:21" ht="13.5" customHeight="1">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -9175,7 +9214,7 @@
       <c r="T199" s="1"/>
       <c r="U199" s="1"/>
     </row>
-    <row r="200" spans="1:21">
+    <row r="200" spans="1:21" ht="13.5" customHeight="1">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -9198,7 +9237,7 @@
       <c r="T200" s="1"/>
       <c r="U200" s="1"/>
     </row>
-    <row r="201" spans="1:21">
+    <row r="201" spans="1:21" ht="13.5" customHeight="1">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -9221,7 +9260,7 @@
       <c r="T201" s="1"/>
       <c r="U201" s="1"/>
     </row>
-    <row r="202" spans="1:21">
+    <row r="202" spans="1:21" ht="13.5" customHeight="1">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -9244,7 +9283,7 @@
       <c r="T202" s="1"/>
       <c r="U202" s="1"/>
     </row>
-    <row r="203" spans="1:21">
+    <row r="203" spans="1:21" ht="13.5" customHeight="1">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -9267,7 +9306,7 @@
       <c r="T203" s="1"/>
       <c r="U203" s="1"/>
     </row>
-    <row r="204" spans="1:21">
+    <row r="204" spans="1:21" ht="13.5" customHeight="1">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -9290,7 +9329,7 @@
       <c r="T204" s="1"/>
       <c r="U204" s="1"/>
     </row>
-    <row r="205" spans="1:21">
+    <row r="205" spans="1:21" ht="13.5" customHeight="1">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -9313,7 +9352,7 @@
       <c r="T205" s="1"/>
       <c r="U205" s="1"/>
     </row>
-    <row r="206" spans="1:21">
+    <row r="206" spans="1:21" ht="13.5" customHeight="1">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -9336,7 +9375,7 @@
       <c r="T206" s="1"/>
       <c r="U206" s="1"/>
     </row>
-    <row r="207" spans="1:21">
+    <row r="207" spans="1:21" ht="13.5" customHeight="1">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -9359,7 +9398,7 @@
       <c r="T207" s="1"/>
       <c r="U207" s="1"/>
     </row>
-    <row r="208" spans="1:21">
+    <row r="208" spans="1:21" ht="13.5" customHeight="1">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -9382,7 +9421,7 @@
       <c r="T208" s="1"/>
       <c r="U208" s="1"/>
     </row>
-    <row r="209" spans="1:21">
+    <row r="209" spans="1:21" ht="13.5" customHeight="1">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -9405,7 +9444,7 @@
       <c r="T209" s="1"/>
       <c r="U209" s="1"/>
     </row>
-    <row r="210" spans="1:21">
+    <row r="210" spans="1:21" ht="13.5" customHeight="1">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -9428,7 +9467,7 @@
       <c r="T210" s="1"/>
       <c r="U210" s="1"/>
     </row>
-    <row r="211" spans="1:21">
+    <row r="211" spans="1:21" ht="13.5" customHeight="1">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -9451,7 +9490,7 @@
       <c r="T211" s="1"/>
       <c r="U211" s="1"/>
     </row>
-    <row r="212" spans="1:21">
+    <row r="212" spans="1:21" ht="13.5" customHeight="1">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -9474,7 +9513,7 @@
       <c r="T212" s="1"/>
       <c r="U212" s="1"/>
     </row>
-    <row r="213" spans="1:21">
+    <row r="213" spans="1:21" ht="13.5" customHeight="1">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -9497,7 +9536,7 @@
       <c r="T213" s="1"/>
       <c r="U213" s="1"/>
     </row>
-    <row r="214" spans="1:21">
+    <row r="214" spans="1:21" ht="13.5" customHeight="1">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -9520,7 +9559,7 @@
       <c r="T214" s="1"/>
       <c r="U214" s="1"/>
     </row>
-    <row r="215" spans="1:21">
+    <row r="215" spans="1:21" ht="13.5" customHeight="1">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -9543,7 +9582,7 @@
       <c r="T215" s="1"/>
       <c r="U215" s="1"/>
     </row>
-    <row r="216" spans="1:21">
+    <row r="216" spans="1:21" ht="13.5" customHeight="1">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -9566,7 +9605,7 @@
       <c r="T216" s="1"/>
       <c r="U216" s="1"/>
     </row>
-    <row r="217" spans="1:21">
+    <row r="217" spans="1:21" ht="13.5" customHeight="1">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -9589,7 +9628,7 @@
       <c r="T217" s="1"/>
       <c r="U217" s="1"/>
     </row>
-    <row r="218" spans="1:21">
+    <row r="218" spans="1:21" ht="13.5" customHeight="1">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -9612,7 +9651,7 @@
       <c r="T218" s="1"/>
       <c r="U218" s="1"/>
     </row>
-    <row r="219" spans="1:21">
+    <row r="219" spans="1:21" ht="13.5" customHeight="1">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -9635,7 +9674,7 @@
       <c r="T219" s="1"/>
       <c r="U219" s="1"/>
     </row>
-    <row r="220" spans="1:21">
+    <row r="220" spans="1:21" ht="13.5" customHeight="1">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -9658,7 +9697,7 @@
       <c r="T220" s="1"/>
       <c r="U220" s="1"/>
     </row>
-    <row r="221" spans="1:21">
+    <row r="221" spans="1:21" ht="13.5" customHeight="1">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -9681,7 +9720,7 @@
       <c r="T221" s="1"/>
       <c r="U221" s="1"/>
     </row>
-    <row r="222" spans="1:21">
+    <row r="222" spans="1:21" ht="13.5" customHeight="1">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -9704,7 +9743,7 @@
       <c r="T222" s="1"/>
       <c r="U222" s="1"/>
     </row>
-    <row r="223" spans="1:21">
+    <row r="223" spans="1:21" ht="13.5" customHeight="1">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -9727,7 +9766,7 @@
       <c r="T223" s="1"/>
       <c r="U223" s="1"/>
     </row>
-    <row r="224" spans="1:21">
+    <row r="224" spans="1:21" ht="13.5" customHeight="1">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -9750,7 +9789,7 @@
       <c r="T224" s="1"/>
       <c r="U224" s="1"/>
     </row>
-    <row r="225" spans="1:21">
+    <row r="225" spans="1:21" ht="13.5" customHeight="1">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -9773,7 +9812,7 @@
       <c r="T225" s="1"/>
       <c r="U225" s="1"/>
     </row>
-    <row r="226" spans="1:21">
+    <row r="226" spans="1:21" ht="13.5" customHeight="1">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -9796,7 +9835,7 @@
       <c r="T226" s="1"/>
       <c r="U226" s="1"/>
     </row>
-    <row r="227" spans="1:21">
+    <row r="227" spans="1:21" ht="13.5" customHeight="1">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -9819,7 +9858,7 @@
       <c r="T227" s="1"/>
       <c r="U227" s="1"/>
     </row>
-    <row r="228" spans="1:21">
+    <row r="228" spans="1:21" ht="13.5" customHeight="1">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -9842,7 +9881,7 @@
       <c r="T228" s="1"/>
       <c r="U228" s="1"/>
     </row>
-    <row r="229" spans="1:21">
+    <row r="229" spans="1:21" ht="13.5" customHeight="1">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -9865,7 +9904,7 @@
       <c r="T229" s="1"/>
       <c r="U229" s="1"/>
     </row>
-    <row r="230" spans="1:21">
+    <row r="230" spans="1:21" ht="13.5" customHeight="1">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -9888,7 +9927,7 @@
       <c r="T230" s="1"/>
       <c r="U230" s="1"/>
     </row>
-    <row r="231" spans="1:21">
+    <row r="231" spans="1:21" ht="13.5" customHeight="1">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -9911,7 +9950,7 @@
       <c r="T231" s="1"/>
       <c r="U231" s="1"/>
     </row>
-    <row r="232" spans="1:21">
+    <row r="232" spans="1:21" ht="13.5" customHeight="1">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -9934,7 +9973,7 @@
       <c r="T232" s="1"/>
       <c r="U232" s="1"/>
     </row>
-    <row r="233" spans="1:21">
+    <row r="233" spans="1:21" ht="13.5" customHeight="1">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -9957,7 +9996,7 @@
       <c r="T233" s="1"/>
       <c r="U233" s="1"/>
     </row>
-    <row r="234" spans="1:21">
+    <row r="234" spans="1:21" ht="13.5" customHeight="1">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -9980,7 +10019,7 @@
       <c r="T234" s="1"/>
       <c r="U234" s="1"/>
     </row>
-    <row r="235" spans="1:21">
+    <row r="235" spans="1:21" ht="13.5" customHeight="1">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -10003,7 +10042,7 @@
       <c r="T235" s="1"/>
       <c r="U235" s="1"/>
     </row>
-    <row r="236" spans="1:21">
+    <row r="236" spans="1:21" ht="13.5" customHeight="1">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -10026,7 +10065,7 @@
       <c r="T236" s="1"/>
       <c r="U236" s="1"/>
     </row>
-    <row r="237" spans="1:21">
+    <row r="237" spans="1:21" ht="13.5" customHeight="1">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -10049,7 +10088,7 @@
       <c r="T237" s="1"/>
       <c r="U237" s="1"/>
     </row>
-    <row r="238" spans="1:21">
+    <row r="238" spans="1:21" ht="13.5" customHeight="1">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -10072,7 +10111,7 @@
       <c r="T238" s="1"/>
       <c r="U238" s="1"/>
     </row>
-    <row r="239" spans="1:21">
+    <row r="239" spans="1:21" ht="13.5" customHeight="1">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -10095,7 +10134,7 @@
       <c r="T239" s="1"/>
       <c r="U239" s="1"/>
     </row>
-    <row r="240" spans="1:21">
+    <row r="240" spans="1:21" ht="13.5" customHeight="1">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -10118,7 +10157,7 @@
       <c r="T240" s="1"/>
       <c r="U240" s="1"/>
     </row>
-    <row r="241" spans="1:21">
+    <row r="241" spans="1:21" ht="13.5" customHeight="1">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -10141,7 +10180,7 @@
       <c r="T241" s="1"/>
       <c r="U241" s="1"/>
     </row>
-    <row r="242" spans="1:21">
+    <row r="242" spans="1:21" ht="13.5" customHeight="1">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -10164,7 +10203,7 @@
       <c r="T242" s="1"/>
       <c r="U242" s="1"/>
     </row>
-    <row r="243" spans="1:21">
+    <row r="243" spans="1:21" ht="13.5" customHeight="1">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -10187,7 +10226,7 @@
       <c r="T243" s="1"/>
       <c r="U243" s="1"/>
     </row>
-    <row r="244" spans="1:21">
+    <row r="244" spans="1:21" ht="13.5" customHeight="1">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -10210,7 +10249,7 @@
       <c r="T244" s="1"/>
       <c r="U244" s="1"/>
     </row>
-    <row r="245" spans="1:21">
+    <row r="245" spans="1:21" ht="13.5" customHeight="1">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -10233,7 +10272,7 @@
       <c r="T245" s="1"/>
       <c r="U245" s="1"/>
     </row>
-    <row r="246" spans="1:21">
+    <row r="246" spans="1:21" ht="13.5" customHeight="1">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -10256,7 +10295,7 @@
       <c r="T246" s="1"/>
       <c r="U246" s="1"/>
     </row>
-    <row r="247" spans="1:21">
+    <row r="247" spans="1:21" ht="13.5" customHeight="1">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -10279,7 +10318,7 @@
       <c r="T247" s="1"/>
       <c r="U247" s="1"/>
     </row>
-    <row r="248" spans="1:21">
+    <row r="248" spans="1:21" ht="13.5" customHeight="1">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -10302,7 +10341,7 @@
       <c r="T248" s="1"/>
       <c r="U248" s="1"/>
     </row>
-    <row r="249" spans="1:21">
+    <row r="249" spans="1:21" ht="13.5" customHeight="1">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -10325,7 +10364,7 @@
       <c r="T249" s="1"/>
       <c r="U249" s="1"/>
     </row>
-    <row r="250" spans="1:21">
+    <row r="250" spans="1:21" ht="13.5" customHeight="1">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -10348,7 +10387,7 @@
       <c r="T250" s="1"/>
       <c r="U250" s="1"/>
     </row>
-    <row r="251" spans="1:21">
+    <row r="251" spans="1:21" ht="13.5" customHeight="1">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -10371,7 +10410,7 @@
       <c r="T251" s="1"/>
       <c r="U251" s="1"/>
     </row>
-    <row r="252" spans="1:21">
+    <row r="252" spans="1:21" ht="13.5" customHeight="1">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -10394,7 +10433,7 @@
       <c r="T252" s="1"/>
       <c r="U252" s="1"/>
     </row>
-    <row r="253" spans="1:21">
+    <row r="253" spans="1:21" ht="13.5" customHeight="1">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -10417,7 +10456,7 @@
       <c r="T253" s="1"/>
       <c r="U253" s="1"/>
     </row>
-    <row r="254" spans="1:21">
+    <row r="254" spans="1:21" ht="13.5" customHeight="1">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -10440,7 +10479,7 @@
       <c r="T254" s="1"/>
       <c r="U254" s="1"/>
     </row>
-    <row r="255" spans="1:21">
+    <row r="255" spans="1:21" ht="13.5" customHeight="1">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -10463,7 +10502,7 @@
       <c r="T255" s="1"/>
       <c r="U255" s="1"/>
     </row>
-    <row r="256" spans="1:21">
+    <row r="256" spans="1:21" ht="13.5" customHeight="1">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -10486,7 +10525,7 @@
       <c r="T256" s="1"/>
       <c r="U256" s="1"/>
     </row>
-    <row r="257" spans="1:21">
+    <row r="257" spans="1:21" ht="13.5" customHeight="1">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -10509,7 +10548,7 @@
       <c r="T257" s="1"/>
       <c r="U257" s="1"/>
     </row>
-    <row r="258" spans="1:21">
+    <row r="258" spans="1:21" ht="13.5" customHeight="1">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -10532,7 +10571,7 @@
       <c r="T258" s="1"/>
       <c r="U258" s="1"/>
     </row>
-    <row r="259" spans="1:21">
+    <row r="259" spans="1:21" ht="13.5" customHeight="1">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -10555,7 +10594,7 @@
       <c r="T259" s="1"/>
       <c r="U259" s="1"/>
     </row>
-    <row r="260" spans="1:21">
+    <row r="260" spans="1:21" ht="13.5" customHeight="1">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -10578,7 +10617,7 @@
       <c r="T260" s="1"/>
       <c r="U260" s="1"/>
     </row>
-    <row r="261" spans="1:21">
+    <row r="261" spans="1:21" ht="13.5" customHeight="1">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -10601,7 +10640,7 @@
       <c r="T261" s="1"/>
       <c r="U261" s="1"/>
     </row>
-    <row r="262" spans="1:21">
+    <row r="262" spans="1:21" ht="13.5" customHeight="1">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -10624,7 +10663,7 @@
       <c r="T262" s="1"/>
       <c r="U262" s="1"/>
     </row>
-    <row r="263" spans="1:21">
+    <row r="263" spans="1:21" ht="13.5" customHeight="1">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -10647,7 +10686,7 @@
       <c r="T263" s="1"/>
       <c r="U263" s="1"/>
     </row>
-    <row r="264" spans="1:21">
+    <row r="264" spans="1:21" ht="13.5" customHeight="1">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -10670,7 +10709,7 @@
       <c r="T264" s="1"/>
       <c r="U264" s="1"/>
     </row>
-    <row r="265" spans="1:21">
+    <row r="265" spans="1:21" ht="13.5" customHeight="1">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -10693,7 +10732,7 @@
       <c r="T265" s="1"/>
       <c r="U265" s="1"/>
     </row>
-    <row r="266" spans="1:21">
+    <row r="266" spans="1:21" ht="13.5" customHeight="1">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -10716,7 +10755,7 @@
       <c r="T266" s="1"/>
       <c r="U266" s="1"/>
     </row>
-    <row r="267" spans="1:21">
+    <row r="267" spans="1:21" ht="13.5" customHeight="1">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -10739,7 +10778,7 @@
       <c r="T267" s="1"/>
       <c r="U267" s="1"/>
     </row>
-    <row r="268" spans="1:21">
+    <row r="268" spans="1:21" ht="13.5" customHeight="1">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -10762,7 +10801,7 @@
       <c r="T268" s="1"/>
       <c r="U268" s="1"/>
     </row>
-    <row r="269" spans="1:21">
+    <row r="269" spans="1:21" ht="13.5" customHeight="1">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -10785,7 +10824,7 @@
       <c r="T269" s="1"/>
       <c r="U269" s="1"/>
     </row>
-    <row r="270" spans="1:21">
+    <row r="270" spans="1:21" ht="13.5" customHeight="1">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -10808,7 +10847,7 @@
       <c r="T270" s="1"/>
       <c r="U270" s="1"/>
     </row>
-    <row r="271" spans="1:21">
+    <row r="271" spans="1:21" ht="13.5" customHeight="1">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -10831,7 +10870,7 @@
       <c r="T271" s="1"/>
       <c r="U271" s="1"/>
     </row>
-    <row r="272" spans="1:21">
+    <row r="272" spans="1:21" ht="13.5" customHeight="1">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -10854,7 +10893,7 @@
       <c r="T272" s="1"/>
       <c r="U272" s="1"/>
     </row>
-    <row r="273" spans="1:21">
+    <row r="273" spans="1:21" ht="13.5" customHeight="1">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -10877,7 +10916,7 @@
       <c r="T273" s="1"/>
       <c r="U273" s="1"/>
     </row>
-    <row r="274" spans="1:21">
+    <row r="274" spans="1:21" ht="13.5" customHeight="1">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -10900,7 +10939,7 @@
       <c r="T274" s="1"/>
       <c r="U274" s="1"/>
     </row>
-    <row r="275" spans="1:21">
+    <row r="275" spans="1:21" ht="13.5" customHeight="1">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -10923,7 +10962,7 @@
       <c r="T275" s="1"/>
       <c r="U275" s="1"/>
     </row>
-    <row r="276" spans="1:21">
+    <row r="276" spans="1:21" ht="13.5" customHeight="1">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -10946,7 +10985,7 @@
       <c r="T276" s="1"/>
       <c r="U276" s="1"/>
     </row>
-    <row r="277" spans="1:21">
+    <row r="277" spans="1:21" ht="13.5" customHeight="1">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -10969,7 +11008,7 @@
       <c r="T277" s="1"/>
       <c r="U277" s="1"/>
     </row>
-    <row r="278" spans="1:21">
+    <row r="278" spans="1:21" ht="13.5" customHeight="1">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -10992,7 +11031,7 @@
       <c r="T278" s="1"/>
       <c r="U278" s="1"/>
     </row>
-    <row r="279" spans="1:21">
+    <row r="279" spans="1:21" ht="13.5" customHeight="1">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -11015,7 +11054,7 @@
       <c r="T279" s="1"/>
       <c r="U279" s="1"/>
     </row>
-    <row r="280" spans="1:21">
+    <row r="280" spans="1:21" ht="13.5" customHeight="1">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -11038,7 +11077,7 @@
       <c r="T280" s="1"/>
       <c r="U280" s="1"/>
     </row>
-    <row r="281" spans="1:21">
+    <row r="281" spans="1:21" ht="13.5" customHeight="1">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -11061,7 +11100,7 @@
       <c r="T281" s="1"/>
       <c r="U281" s="1"/>
     </row>
-    <row r="282" spans="1:21">
+    <row r="282" spans="1:21" ht="13.5" customHeight="1">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -11084,7 +11123,7 @@
       <c r="T282" s="1"/>
       <c r="U282" s="1"/>
     </row>
-    <row r="283" spans="1:21">
+    <row r="283" spans="1:21" ht="13.5" customHeight="1">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -11107,7 +11146,7 @@
       <c r="T283" s="1"/>
       <c r="U283" s="1"/>
     </row>
-    <row r="284" spans="1:21">
+    <row r="284" spans="1:21" ht="13.5" customHeight="1">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -11130,7 +11169,7 @@
       <c r="T284" s="1"/>
       <c r="U284" s="1"/>
     </row>
-    <row r="285" spans="1:21">
+    <row r="285" spans="1:21" ht="13.5" customHeight="1">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -11153,7 +11192,7 @@
       <c r="T285" s="1"/>
       <c r="U285" s="1"/>
     </row>
-    <row r="286" spans="1:21">
+    <row r="286" spans="1:21" ht="13.5" customHeight="1">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -11176,7 +11215,7 @@
       <c r="T286" s="1"/>
       <c r="U286" s="1"/>
     </row>
-    <row r="287" spans="1:21">
+    <row r="287" spans="1:21" ht="13.5" customHeight="1">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -11199,7 +11238,7 @@
       <c r="T287" s="1"/>
       <c r="U287" s="1"/>
     </row>
-    <row r="288" spans="1:21">
+    <row r="288" spans="1:21" ht="13.5" customHeight="1">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -11222,7 +11261,7 @@
       <c r="T288" s="1"/>
       <c r="U288" s="1"/>
     </row>
-    <row r="289" spans="1:21">
+    <row r="289" spans="1:21" ht="13.5" customHeight="1">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -11245,7 +11284,7 @@
       <c r="T289" s="1"/>
       <c r="U289" s="1"/>
     </row>
-    <row r="290" spans="1:21">
+    <row r="290" spans="1:21" ht="13.5" customHeight="1">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -11268,7 +11307,7 @@
       <c r="T290" s="1"/>
       <c r="U290" s="1"/>
     </row>
-    <row r="291" spans="1:21">
+    <row r="291" spans="1:21" ht="13.5" customHeight="1">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -11291,7 +11330,7 @@
       <c r="T291" s="1"/>
       <c r="U291" s="1"/>
     </row>
-    <row r="292" spans="1:21">
+    <row r="292" spans="1:21" ht="13.5" customHeight="1">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -11314,7 +11353,7 @@
       <c r="T292" s="1"/>
       <c r="U292" s="1"/>
     </row>
-    <row r="293" spans="1:21">
+    <row r="293" spans="1:21" ht="13.5" customHeight="1">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -11337,7 +11376,7 @@
       <c r="T293" s="1"/>
       <c r="U293" s="1"/>
     </row>
-    <row r="294" spans="1:21">
+    <row r="294" spans="1:21" ht="13.5" customHeight="1">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -11360,7 +11399,7 @@
       <c r="T294" s="1"/>
       <c r="U294" s="1"/>
     </row>
-    <row r="295" spans="1:21">
+    <row r="295" spans="1:21" ht="13.5" customHeight="1">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -11383,7 +11422,7 @@
       <c r="T295" s="1"/>
       <c r="U295" s="1"/>
     </row>
-    <row r="296" spans="1:21">
+    <row r="296" spans="1:21" ht="13.5" customHeight="1">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -11406,7 +11445,7 @@
       <c r="T296" s="1"/>
       <c r="U296" s="1"/>
     </row>
-    <row r="297" spans="1:21">
+    <row r="297" spans="1:21" ht="13.5" customHeight="1">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -11429,7 +11468,7 @@
       <c r="T297" s="1"/>
       <c r="U297" s="1"/>
     </row>
-    <row r="298" spans="1:21">
+    <row r="298" spans="1:21" ht="13.5" customHeight="1">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -11452,7 +11491,7 @@
       <c r="T298" s="1"/>
       <c r="U298" s="1"/>
     </row>
-    <row r="299" spans="1:21">
+    <row r="299" spans="1:21" ht="13.5" customHeight="1">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -11475,7 +11514,7 @@
       <c r="T299" s="1"/>
       <c r="U299" s="1"/>
     </row>
-    <row r="300" spans="1:21">
+    <row r="300" spans="1:21" ht="13.5" customHeight="1">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -11498,7 +11537,7 @@
       <c r="T300" s="1"/>
       <c r="U300" s="1"/>
     </row>
-    <row r="301" spans="1:21">
+    <row r="301" spans="1:21" ht="13.5" customHeight="1">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -11521,7 +11560,7 @@
       <c r="T301" s="1"/>
       <c r="U301" s="1"/>
     </row>
-    <row r="302" spans="1:21">
+    <row r="302" spans="1:21" ht="13.5" customHeight="1">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -11544,7 +11583,7 @@
       <c r="T302" s="1"/>
       <c r="U302" s="1"/>
     </row>
-    <row r="303" spans="1:21">
+    <row r="303" spans="1:21" ht="13.5" customHeight="1">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -11567,7 +11606,7 @@
       <c r="T303" s="1"/>
       <c r="U303" s="1"/>
     </row>
-    <row r="304" spans="1:21">
+    <row r="304" spans="1:21" ht="13.5" customHeight="1">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -11590,7 +11629,7 @@
       <c r="T304" s="1"/>
       <c r="U304" s="1"/>
     </row>
-    <row r="305" spans="1:21">
+    <row r="305" spans="1:21" ht="13.5" customHeight="1">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -11613,7 +11652,7 @@
       <c r="T305" s="1"/>
       <c r="U305" s="1"/>
     </row>
-    <row r="306" spans="1:21">
+    <row r="306" spans="1:21" ht="13.5" customHeight="1">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -11636,7 +11675,7 @@
       <c r="T306" s="1"/>
       <c r="U306" s="1"/>
     </row>
-    <row r="307" spans="1:21">
+    <row r="307" spans="1:21" ht="13.5" customHeight="1">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -11659,7 +11698,7 @@
       <c r="T307" s="1"/>
       <c r="U307" s="1"/>
     </row>
-    <row r="308" spans="1:21">
+    <row r="308" spans="1:21" ht="13.5" customHeight="1">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -11682,7 +11721,7 @@
       <c r="T308" s="1"/>
       <c r="U308" s="1"/>
     </row>
-    <row r="309" spans="1:21">
+    <row r="309" spans="1:21" ht="13.5" customHeight="1">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -11705,7 +11744,7 @@
       <c r="T309" s="1"/>
       <c r="U309" s="1"/>
     </row>
-    <row r="310" spans="1:21">
+    <row r="310" spans="1:21" ht="13.5" customHeight="1">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -11728,7 +11767,7 @@
       <c r="T310" s="1"/>
       <c r="U310" s="1"/>
     </row>
-    <row r="311" spans="1:21">
+    <row r="311" spans="1:21" ht="13.5" customHeight="1">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -11751,7 +11790,7 @@
       <c r="T311" s="1"/>
       <c r="U311" s="1"/>
     </row>
-    <row r="312" spans="1:21">
+    <row r="312" spans="1:21" ht="13.5" customHeight="1">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -11774,7 +11813,7 @@
       <c r="T312" s="1"/>
       <c r="U312" s="1"/>
     </row>
-    <row r="313" spans="1:21">
+    <row r="313" spans="1:21" ht="13.5" customHeight="1">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -11797,7 +11836,7 @@
       <c r="T313" s="1"/>
       <c r="U313" s="1"/>
     </row>
-    <row r="314" spans="1:21">
+    <row r="314" spans="1:21" ht="13.5" customHeight="1">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -11820,7 +11859,7 @@
       <c r="T314" s="1"/>
       <c r="U314" s="1"/>
     </row>
-    <row r="315" spans="1:21">
+    <row r="315" spans="1:21" ht="13.5" customHeight="1">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -11843,7 +11882,7 @@
       <c r="T315" s="1"/>
       <c r="U315" s="1"/>
     </row>
-    <row r="316" spans="1:21">
+    <row r="316" spans="1:21" ht="13.5" customHeight="1">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -11866,7 +11905,7 @@
       <c r="T316" s="1"/>
       <c r="U316" s="1"/>
     </row>
-    <row r="317" spans="1:21">
+    <row r="317" spans="1:21" ht="13.5" customHeight="1">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -11889,7 +11928,7 @@
       <c r="T317" s="1"/>
       <c r="U317" s="1"/>
     </row>
-    <row r="318" spans="1:21">
+    <row r="318" spans="1:21" ht="13.5" customHeight="1">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -11912,7 +11951,7 @@
       <c r="T318" s="1"/>
       <c r="U318" s="1"/>
     </row>
-    <row r="319" spans="1:21">
+    <row r="319" spans="1:21" ht="13.5" customHeight="1">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -11935,7 +11974,7 @@
       <c r="T319" s="1"/>
       <c r="U319" s="1"/>
     </row>
-    <row r="320" spans="1:21">
+    <row r="320" spans="1:21" ht="13.5" customHeight="1">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -11958,7 +11997,7 @@
       <c r="T320" s="1"/>
       <c r="U320" s="1"/>
     </row>
-    <row r="321" spans="1:21">
+    <row r="321" spans="1:21" ht="13.5" customHeight="1">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -11981,7 +12020,7 @@
       <c r="T321" s="1"/>
       <c r="U321" s="1"/>
     </row>
-    <row r="322" spans="1:21">
+    <row r="322" spans="1:21" ht="13.5" customHeight="1">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -12004,7 +12043,7 @@
       <c r="T322" s="1"/>
       <c r="U322" s="1"/>
     </row>
-    <row r="323" spans="1:21">
+    <row r="323" spans="1:21" ht="13.5" customHeight="1">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -12027,7 +12066,7 @@
       <c r="T323" s="1"/>
       <c r="U323" s="1"/>
     </row>
-    <row r="324" spans="1:21">
+    <row r="324" spans="1:21" ht="13.5" customHeight="1">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -12050,7 +12089,7 @@
       <c r="T324" s="1"/>
       <c r="U324" s="1"/>
     </row>
-    <row r="325" spans="1:21">
+    <row r="325" spans="1:21" ht="13.5" customHeight="1">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -12073,7 +12112,7 @@
       <c r="T325" s="1"/>
       <c r="U325" s="1"/>
     </row>
-    <row r="326" spans="1:21">
+    <row r="326" spans="1:21" ht="13.5" customHeight="1">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -12096,7 +12135,7 @@
       <c r="T326" s="1"/>
       <c r="U326" s="1"/>
     </row>
-    <row r="327" spans="1:21">
+    <row r="327" spans="1:21" ht="13.5" customHeight="1">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -12119,7 +12158,7 @@
       <c r="T327" s="1"/>
       <c r="U327" s="1"/>
     </row>
-    <row r="328" spans="1:21">
+    <row r="328" spans="1:21" ht="13.5" customHeight="1">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -12142,7 +12181,7 @@
       <c r="T328" s="1"/>
       <c r="U328" s="1"/>
     </row>
-    <row r="329" spans="1:21">
+    <row r="329" spans="1:21" ht="13.5" customHeight="1">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -12165,7 +12204,7 @@
       <c r="T329" s="1"/>
       <c r="U329" s="1"/>
     </row>
-    <row r="330" spans="1:21">
+    <row r="330" spans="1:21" ht="13.5" customHeight="1">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -12188,7 +12227,7 @@
       <c r="T330" s="1"/>
       <c r="U330" s="1"/>
     </row>
-    <row r="331" spans="1:21">
+    <row r="331" spans="1:21" ht="13.5" customHeight="1">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -12211,7 +12250,7 @@
       <c r="T331" s="1"/>
       <c r="U331" s="1"/>
     </row>
-    <row r="332" spans="1:21">
+    <row r="332" spans="1:21" ht="13.5" customHeight="1">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -12234,7 +12273,7 @@
       <c r="T332" s="1"/>
       <c r="U332" s="1"/>
     </row>
-    <row r="333" spans="1:21">
+    <row r="333" spans="1:21" ht="13.5" customHeight="1">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -12257,7 +12296,7 @@
       <c r="T333" s="1"/>
       <c r="U333" s="1"/>
     </row>
-    <row r="334" spans="1:21">
+    <row r="334" spans="1:21" ht="13.5" customHeight="1">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -12280,7 +12319,7 @@
       <c r="T334" s="1"/>
       <c r="U334" s="1"/>
     </row>
-    <row r="335" spans="1:21">
+    <row r="335" spans="1:21" ht="13.5" customHeight="1">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -12303,7 +12342,7 @@
       <c r="T335" s="1"/>
       <c r="U335" s="1"/>
     </row>
-    <row r="336" spans="1:21">
+    <row r="336" spans="1:21" ht="13.5" customHeight="1">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -12326,7 +12365,7 @@
       <c r="T336" s="1"/>
       <c r="U336" s="1"/>
     </row>
-    <row r="337" spans="1:21">
+    <row r="337" spans="1:21" ht="13.5" customHeight="1">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -12349,7 +12388,7 @@
       <c r="T337" s="1"/>
       <c r="U337" s="1"/>
     </row>
-    <row r="338" spans="1:21">
+    <row r="338" spans="1:21" ht="13.5" customHeight="1">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -12372,7 +12411,7 @@
       <c r="T338" s="1"/>
       <c r="U338" s="1"/>
     </row>
-    <row r="339" spans="1:21">
+    <row r="339" spans="1:21" ht="13.5" customHeight="1">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -12395,7 +12434,7 @@
       <c r="T339" s="1"/>
       <c r="U339" s="1"/>
     </row>
-    <row r="340" spans="1:21">
+    <row r="340" spans="1:21" ht="13.5" customHeight="1">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -12418,7 +12457,7 @@
       <c r="T340" s="1"/>
       <c r="U340" s="1"/>
     </row>
-    <row r="341" spans="1:21">
+    <row r="341" spans="1:21" ht="13.5" customHeight="1">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -12441,7 +12480,7 @@
       <c r="T341" s="1"/>
       <c r="U341" s="1"/>
     </row>
-    <row r="342" spans="1:21">
+    <row r="342" spans="1:21" ht="13.5" customHeight="1">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -12464,7 +12503,7 @@
       <c r="T342" s="1"/>
       <c r="U342" s="1"/>
     </row>
-    <row r="343" spans="1:21">
+    <row r="343" spans="1:21" ht="13.5" customHeight="1">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -12487,7 +12526,7 @@
       <c r="T343" s="1"/>
       <c r="U343" s="1"/>
     </row>
-    <row r="344" spans="1:21">
+    <row r="344" spans="1:21" ht="13.5" customHeight="1">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -12510,7 +12549,7 @@
       <c r="T344" s="1"/>
       <c r="U344" s="1"/>
     </row>
-    <row r="345" spans="1:21">
+    <row r="345" spans="1:21" ht="13.5" customHeight="1">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -12533,7 +12572,7 @@
       <c r="T345" s="1"/>
       <c r="U345" s="1"/>
     </row>
-    <row r="346" spans="1:21">
+    <row r="346" spans="1:21" ht="13.5" customHeight="1">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -12556,7 +12595,7 @@
       <c r="T346" s="1"/>
       <c r="U346" s="1"/>
     </row>
-    <row r="347" spans="1:21">
+    <row r="347" spans="1:21" ht="13.5" customHeight="1">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -12579,7 +12618,7 @@
       <c r="T347" s="1"/>
       <c r="U347" s="1"/>
     </row>
-    <row r="348" spans="1:21">
+    <row r="348" spans="1:21" ht="13.5" customHeight="1">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -12602,7 +12641,7 @@
       <c r="T348" s="1"/>
       <c r="U348" s="1"/>
     </row>
-    <row r="349" spans="1:21">
+    <row r="349" spans="1:21" ht="13.5" customHeight="1">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -12625,7 +12664,7 @@
       <c r="T349" s="1"/>
       <c r="U349" s="1"/>
     </row>
-    <row r="350" spans="1:21">
+    <row r="350" spans="1:21" ht="13.5" customHeight="1">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -12648,7 +12687,7 @@
       <c r="T350" s="1"/>
       <c r="U350" s="1"/>
     </row>
-    <row r="351" spans="1:21">
+    <row r="351" spans="1:21" ht="13.5" customHeight="1">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -12671,7 +12710,7 @@
       <c r="T351" s="1"/>
       <c r="U351" s="1"/>
     </row>
-    <row r="352" spans="1:21">
+    <row r="352" spans="1:21" ht="13.5" customHeight="1">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -12694,7 +12733,7 @@
       <c r="T352" s="1"/>
       <c r="U352" s="1"/>
     </row>
-    <row r="353" spans="1:21">
+    <row r="353" spans="1:21" ht="13.5" customHeight="1">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -12717,7 +12756,7 @@
       <c r="T353" s="1"/>
       <c r="U353" s="1"/>
     </row>
-    <row r="354" spans="1:21">
+    <row r="354" spans="1:21" ht="13.5" customHeight="1">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -12740,7 +12779,7 @@
       <c r="T354" s="1"/>
       <c r="U354" s="1"/>
     </row>
-    <row r="355" spans="1:21">
+    <row r="355" spans="1:21" ht="13.5" customHeight="1">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -12763,7 +12802,7 @@
       <c r="T355" s="1"/>
       <c r="U355" s="1"/>
     </row>
-    <row r="356" spans="1:21">
+    <row r="356" spans="1:21" ht="13.5" customHeight="1">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -12786,7 +12825,7 @@
       <c r="T356" s="1"/>
       <c r="U356" s="1"/>
     </row>
-    <row r="357" spans="1:21">
+    <row r="357" spans="1:21" ht="13.5" customHeight="1">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -12809,7 +12848,7 @@
       <c r="T357" s="1"/>
       <c r="U357" s="1"/>
     </row>
-    <row r="358" spans="1:21">
+    <row r="358" spans="1:21" ht="13.5" customHeight="1">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -12832,7 +12871,7 @@
       <c r="T358" s="1"/>
       <c r="U358" s="1"/>
     </row>
-    <row r="359" spans="1:21">
+    <row r="359" spans="1:21" ht="13.5" customHeight="1">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -12855,7 +12894,7 @@
       <c r="T359" s="1"/>
       <c r="U359" s="1"/>
     </row>
-    <row r="360" spans="1:21">
+    <row r="360" spans="1:21" ht="13.5" customHeight="1">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -12878,7 +12917,7 @@
       <c r="T360" s="1"/>
       <c r="U360" s="1"/>
     </row>
-    <row r="361" spans="1:21">
+    <row r="361" spans="1:21" ht="13.5" customHeight="1">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -12901,7 +12940,7 @@
       <c r="T361" s="1"/>
       <c r="U361" s="1"/>
     </row>
-    <row r="362" spans="1:21">
+    <row r="362" spans="1:21" ht="13.5" customHeight="1">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -12924,7 +12963,7 @@
       <c r="T362" s="1"/>
       <c r="U362" s="1"/>
     </row>
-    <row r="363" spans="1:21">
+    <row r="363" spans="1:21" ht="13.5" customHeight="1">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -12947,7 +12986,7 @@
       <c r="T363" s="1"/>
       <c r="U363" s="1"/>
     </row>
-    <row r="364" spans="1:21">
+    <row r="364" spans="1:21" ht="13.5" customHeight="1">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -12970,7 +13009,7 @@
       <c r="T364" s="1"/>
       <c r="U364" s="1"/>
     </row>
-    <row r="365" spans="1:21">
+    <row r="365" spans="1:21" ht="13.5" customHeight="1">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -12993,7 +13032,7 @@
       <c r="T365" s="1"/>
       <c r="U365" s="1"/>
     </row>
-    <row r="366" spans="1:21">
+    <row r="366" spans="1:21" ht="13.5" customHeight="1">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -13016,7 +13055,7 @@
       <c r="T366" s="1"/>
       <c r="U366" s="1"/>
     </row>
-    <row r="367" spans="1:21">
+    <row r="367" spans="1:21" ht="13.5" customHeight="1">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -13039,7 +13078,7 @@
       <c r="T367" s="1"/>
       <c r="U367" s="1"/>
     </row>
-    <row r="368" spans="1:21">
+    <row r="368" spans="1:21" ht="13.5" customHeight="1">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -13062,7 +13101,7 @@
       <c r="T368" s="1"/>
       <c r="U368" s="1"/>
     </row>
-    <row r="369" spans="1:21">
+    <row r="369" spans="1:21" ht="13.5" customHeight="1">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -13085,7 +13124,7 @@
       <c r="T369" s="1"/>
       <c r="U369" s="1"/>
     </row>
-    <row r="370" spans="1:21">
+    <row r="370" spans="1:21" ht="13.5" customHeight="1">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -13108,7 +13147,7 @@
       <c r="T370" s="1"/>
       <c r="U370" s="1"/>
     </row>
-    <row r="371" spans="1:21">
+    <row r="371" spans="1:21" ht="13.5" customHeight="1">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -13131,7 +13170,7 @@
       <c r="T371" s="1"/>
       <c r="U371" s="1"/>
     </row>
-    <row r="372" spans="1:21">
+    <row r="372" spans="1:21" ht="13.5" customHeight="1">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -13154,7 +13193,7 @@
       <c r="T372" s="1"/>
       <c r="U372" s="1"/>
     </row>
-    <row r="373" spans="1:21">
+    <row r="373" spans="1:21" ht="13.5" customHeight="1">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -13177,7 +13216,7 @@
       <c r="T373" s="1"/>
       <c r="U373" s="1"/>
     </row>
-    <row r="374" spans="1:21">
+    <row r="374" spans="1:21" ht="13.5" customHeight="1">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -13200,7 +13239,7 @@
       <c r="T374" s="1"/>
       <c r="U374" s="1"/>
     </row>
-    <row r="375" spans="1:21">
+    <row r="375" spans="1:21" ht="13.5" customHeight="1">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -13223,7 +13262,7 @@
       <c r="T375" s="1"/>
       <c r="U375" s="1"/>
     </row>
-    <row r="376" spans="1:21">
+    <row r="376" spans="1:21" ht="13.5" customHeight="1">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -13246,7 +13285,7 @@
       <c r="T376" s="1"/>
       <c r="U376" s="1"/>
     </row>
-    <row r="377" spans="1:21">
+    <row r="377" spans="1:21" ht="13.5" customHeight="1">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -13269,7 +13308,7 @@
       <c r="T377" s="1"/>
       <c r="U377" s="1"/>
     </row>
-    <row r="378" spans="1:21">
+    <row r="378" spans="1:21" ht="13.5" customHeight="1">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -13292,7 +13331,7 @@
       <c r="T378" s="1"/>
       <c r="U378" s="1"/>
     </row>
-    <row r="379" spans="1:21">
+    <row r="379" spans="1:21" ht="13.5" customHeight="1">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -13315,7 +13354,7 @@
       <c r="T379" s="1"/>
       <c r="U379" s="1"/>
     </row>
-    <row r="380" spans="1:21">
+    <row r="380" spans="1:21" ht="13.5" customHeight="1">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -13338,7 +13377,7 @@
       <c r="T380" s="1"/>
       <c r="U380" s="1"/>
     </row>
-    <row r="381" spans="1:21">
+    <row r="381" spans="1:21" ht="13.5" customHeight="1">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -13361,7 +13400,7 @@
       <c r="T381" s="1"/>
       <c r="U381" s="1"/>
     </row>
-    <row r="382" spans="1:21">
+    <row r="382" spans="1:21" ht="13.5" customHeight="1">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -13384,7 +13423,7 @@
       <c r="T382" s="1"/>
       <c r="U382" s="1"/>
     </row>
-    <row r="383" spans="1:21">
+    <row r="383" spans="1:21" ht="13.5" customHeight="1">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -13407,7 +13446,7 @@
       <c r="T383" s="1"/>
       <c r="U383" s="1"/>
     </row>
-    <row r="384" spans="1:21">
+    <row r="384" spans="1:21" ht="13.5" customHeight="1">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -13430,7 +13469,7 @@
       <c r="T384" s="1"/>
       <c r="U384" s="1"/>
     </row>
-    <row r="385" spans="1:21">
+    <row r="385" spans="1:21" ht="13.5" customHeight="1">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -13453,7 +13492,7 @@
       <c r="T385" s="1"/>
       <c r="U385" s="1"/>
     </row>
-    <row r="386" spans="1:21">
+    <row r="386" spans="1:21" ht="13.5" customHeight="1">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -13476,7 +13515,7 @@
       <c r="T386" s="1"/>
       <c r="U386" s="1"/>
     </row>
-    <row r="387" spans="1:21">
+    <row r="387" spans="1:21" ht="13.5" customHeight="1">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -13499,7 +13538,7 @@
       <c r="T387" s="1"/>
       <c r="U387" s="1"/>
     </row>
-    <row r="388" spans="1:21">
+    <row r="388" spans="1:21" ht="13.5" customHeight="1">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -13522,7 +13561,7 @@
       <c r="T388" s="1"/>
       <c r="U388" s="1"/>
     </row>
-    <row r="389" spans="1:21">
+    <row r="389" spans="1:21" ht="13.5" customHeight="1">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -13545,7 +13584,7 @@
       <c r="T389" s="1"/>
       <c r="U389" s="1"/>
     </row>
-    <row r="390" spans="1:21">
+    <row r="390" spans="1:21" ht="13.5" customHeight="1">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -13568,7 +13607,7 @@
       <c r="T390" s="1"/>
       <c r="U390" s="1"/>
     </row>
-    <row r="391" spans="1:21">
+    <row r="391" spans="1:21" ht="13.5" customHeight="1">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -13591,7 +13630,7 @@
       <c r="T391" s="1"/>
       <c r="U391" s="1"/>
     </row>
-    <row r="392" spans="1:21">
+    <row r="392" spans="1:21" ht="13.5" customHeight="1">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -13614,7 +13653,7 @@
       <c r="T392" s="1"/>
       <c r="U392" s="1"/>
     </row>
-    <row r="393" spans="1:21">
+    <row r="393" spans="1:21" ht="13.5" customHeight="1">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -13637,7 +13676,7 @@
       <c r="T393" s="1"/>
       <c r="U393" s="1"/>
     </row>
-    <row r="394" spans="1:21">
+    <row r="394" spans="1:21" ht="13.5" customHeight="1">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -13660,7 +13699,7 @@
       <c r="T394" s="1"/>
       <c r="U394" s="1"/>
     </row>
-    <row r="395" spans="1:21">
+    <row r="395" spans="1:21" ht="13.5" customHeight="1">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -13683,7 +13722,7 @@
       <c r="T395" s="1"/>
       <c r="U395" s="1"/>
     </row>
-    <row r="396" spans="1:21">
+    <row r="396" spans="1:21" ht="13.5" customHeight="1">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -13706,7 +13745,7 @@
       <c r="T396" s="1"/>
       <c r="U396" s="1"/>
     </row>
-    <row r="397" spans="1:21">
+    <row r="397" spans="1:21" ht="13.5" customHeight="1">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -13729,7 +13768,7 @@
       <c r="T397" s="1"/>
       <c r="U397" s="1"/>
     </row>
-    <row r="398" spans="1:21">
+    <row r="398" spans="1:21" ht="13.5" customHeight="1">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -13752,7 +13791,7 @@
       <c r="T398" s="1"/>
       <c r="U398" s="1"/>
     </row>
-    <row r="399" spans="1:21">
+    <row r="399" spans="1:21" ht="13.5" customHeight="1">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -13775,7 +13814,7 @@
       <c r="T399" s="1"/>
       <c r="U399" s="1"/>
     </row>
-    <row r="400" spans="1:21">
+    <row r="400" spans="1:21" ht="13.5" customHeight="1">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -13798,7 +13837,7 @@
       <c r="T400" s="1"/>
       <c r="U400" s="1"/>
     </row>
-    <row r="401" spans="1:21">
+    <row r="401" spans="1:21" ht="13.5" customHeight="1">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -13821,7 +13860,7 @@
       <c r="T401" s="1"/>
       <c r="U401" s="1"/>
     </row>
-    <row r="402" spans="1:21">
+    <row r="402" spans="1:21" ht="13.5" customHeight="1">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -13844,7 +13883,7 @@
       <c r="T402" s="1"/>
       <c r="U402" s="1"/>
     </row>
-    <row r="403" spans="1:21">
+    <row r="403" spans="1:21" ht="13.5" customHeight="1">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -13867,7 +13906,7 @@
       <c r="T403" s="1"/>
       <c r="U403" s="1"/>
     </row>
-    <row r="404" spans="1:21">
+    <row r="404" spans="1:21" ht="13.5" customHeight="1">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -13890,14 +13929,37 @@
       <c r="T404" s="1"/>
       <c r="U404" s="1"/>
     </row>
-    <row r="405" spans="1:21">
+    <row r="405" spans="1:21" ht="13.5" customHeight="1">
+      <c r="A405" s="1"/>
       <c r="B405" s="1"/>
-    </row>
-    <row r="406" spans="1:21">
+      <c r="C405" s="1"/>
+      <c r="D405" s="1"/>
+      <c r="E405" s="1"/>
+      <c r="F405" s="1"/>
+      <c r="G405" s="1"/>
+      <c r="H405" s="80"/>
+      <c r="I405" s="81"/>
+      <c r="J405" s="1"/>
+      <c r="K405" s="1"/>
+      <c r="L405" s="1"/>
+      <c r="M405" s="56"/>
+      <c r="N405" s="56"/>
+      <c r="O405" s="56"/>
+      <c r="P405" s="56"/>
+      <c r="Q405" s="56"/>
+      <c r="R405" s="56"/>
+      <c r="S405" s="1"/>
+      <c r="T405" s="1"/>
+      <c r="U405" s="1"/>
+    </row>
+    <row r="406" spans="1:21" ht="13.5" customHeight="1">
       <c r="B406" s="1"/>
     </row>
-    <row r="407" spans="1:21">
+    <row r="407" spans="1:21" ht="13.5" customHeight="1">
       <c r="B407" s="1"/>
+    </row>
+    <row r="408" spans="1:21" ht="13.5" customHeight="1">
+      <c r="B408" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -13910,7 +13972,7 @@
     <mergeCell ref="N19:P19"/>
     <mergeCell ref="Q19:S19"/>
   </mergeCells>
-  <conditionalFormatting sqref="D21:D38 D4:D16">
+  <conditionalFormatting sqref="D4:D16 D21:D39">
     <cfRule type="containsText" dxfId="26" priority="41" operator="containsText" text="Approved">
       <formula>NOT(ISERROR(SEARCH("Approved",D4)))</formula>
     </cfRule>
@@ -13933,7 +13995,7 @@
       <formula>NOT(ISERROR(SEARCH("In Progress",D4)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D22:D38 D5:D16">
+  <conditionalFormatting sqref="D5:D16 D22:D39">
     <cfRule type="cellIs" dxfId="19" priority="33" operator="equal">
       <formula>"No Iniciado"</formula>
     </cfRule>
@@ -13959,7 +14021,7 @@
       <formula>"Completo"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S22:S38 S5:S17">
+  <conditionalFormatting sqref="S22:S39 S5:S17">
     <cfRule type="cellIs" dxfId="11" priority="61" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -13988,7 +14050,7 @@
           <x14:formula1>
             <xm:f>'listas desplegables'!$F$3:$F$11</xm:f>
           </x14:formula1>
-          <xm:sqref>D21:D38 D4:D16</xm:sqref>
+          <xm:sqref>D4:D16 D21:D39</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -14014,7 +14076,7 @@
   <sheetData>
     <row r="1" spans="1:32" s="5" customFormat="1" ht="42" customHeight="1" thickBot="1">
       <c r="B1" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
@@ -14043,45 +14105,45 @@
     <row r="2" spans="1:32" ht="24.95" customHeight="1" thickTop="1">
       <c r="A2" s="4"/>
       <c r="B2" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="24" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="24" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2" s="4"/>
     </row>
     <row r="3" spans="1:32" ht="35.1" customHeight="1">
       <c r="A3" s="4"/>
       <c r="B3" s="23" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="22" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="32" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="G3" s="4"/>
     </row>
     <row r="4" spans="1:32" ht="35.1" customHeight="1">
       <c r="A4" s="4"/>
       <c r="B4" s="21" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="20" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="33" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -14089,11 +14151,11 @@
       <c r="A5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="19" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="34" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="G5" s="4"/>
     </row>
@@ -14103,7 +14165,7 @@
       <c r="D6" s="15"/>
       <c r="E6" s="4"/>
       <c r="F6" s="18" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G6" s="4"/>
     </row>
@@ -14113,7 +14175,7 @@
       <c r="D7" s="15"/>
       <c r="E7" s="4"/>
       <c r="F7" s="17" t="s">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c r="G7" s="4"/>
     </row>
@@ -14122,7 +14184,7 @@
       <c r="C8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G8" s="4"/>
     </row>
@@ -14132,7 +14194,7 @@
       <c r="C9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G9" s="4"/>
     </row>
